--- a/Design/config/SkillConfig.xlsx
+++ b/Design/config/SkillConfig.xlsx
@@ -13,7 +13,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$AP$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$AR$84</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="639">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -649,10 +649,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>MagicChargeYellow</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>zhang</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -901,10 +897,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>SoftFireBigRed</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>NukeMissileFires</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1003,10 +995,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>HitEffect</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>jumpspin</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2513,6 +2501,34 @@
   </si>
   <si>
     <t>AttackPointReduce</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>区域</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cs</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectSelf</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectArea</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>EffectHit</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4293,45 +4309,61 @@
           <cell r="R5" t="str">
             <v>帅</v>
           </cell>
+          <cell r="S5"/>
           <cell r="T5" t="str">
             <v>仁</v>
           </cell>
+          <cell r="U5"/>
         </row>
         <row r="6">
           <cell r="R6" t="str">
             <v>帅</v>
           </cell>
+          <cell r="S6"/>
           <cell r="T6" t="str">
             <v>识</v>
           </cell>
+          <cell r="U6"/>
         </row>
         <row r="7">
           <cell r="R7" t="str">
             <v>帅</v>
           </cell>
+          <cell r="S7"/>
           <cell r="T7" t="str">
             <v>衡</v>
           </cell>
+          <cell r="U7"/>
         </row>
         <row r="8">
           <cell r="R8" t="str">
             <v>帅</v>
           </cell>
+          <cell r="S8"/>
+          <cell r="T8"/>
+          <cell r="U8"/>
         </row>
         <row r="9">
           <cell r="R9" t="str">
             <v>帅</v>
           </cell>
+          <cell r="S9"/>
+          <cell r="T9"/>
+          <cell r="U9"/>
         </row>
         <row r="10">
           <cell r="R10" t="str">
             <v>帅</v>
           </cell>
+          <cell r="S10"/>
+          <cell r="T10"/>
+          <cell r="U10"/>
         </row>
         <row r="11">
           <cell r="R11" t="str">
             <v>马</v>
           </cell>
+          <cell r="S11"/>
           <cell r="T11" t="str">
             <v>镜</v>
           </cell>
@@ -4343,22 +4375,27 @@
           <cell r="R12" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S12"/>
           <cell r="T12" t="str">
             <v>威</v>
           </cell>
+          <cell r="U12"/>
         </row>
         <row r="13">
           <cell r="R13" t="str">
             <v>马</v>
           </cell>
+          <cell r="S13"/>
           <cell r="T13" t="str">
             <v>铁</v>
           </cell>
+          <cell r="U13"/>
         </row>
         <row r="14">
           <cell r="R14" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S14"/>
           <cell r="T14" t="str">
             <v>神</v>
           </cell>
@@ -4370,14 +4407,17 @@
           <cell r="R15" t="str">
             <v>车</v>
           </cell>
+          <cell r="S15"/>
           <cell r="T15" t="str">
             <v>斩</v>
           </cell>
+          <cell r="U15"/>
         </row>
         <row r="16">
           <cell r="R16" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S16"/>
           <cell r="T16" t="str">
             <v>火</v>
           </cell>
@@ -4389,6 +4429,7 @@
           <cell r="R17" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S17"/>
           <cell r="T17" t="str">
             <v>破</v>
           </cell>
@@ -4400,6 +4441,7 @@
           <cell r="R18" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S18"/>
           <cell r="T18" t="str">
             <v>矢</v>
           </cell>
@@ -4411,22 +4453,27 @@
           <cell r="R19" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S19"/>
           <cell r="T19" t="str">
             <v>劫</v>
           </cell>
+          <cell r="U19"/>
         </row>
         <row r="20">
           <cell r="R20" t="str">
             <v>车</v>
           </cell>
+          <cell r="S20"/>
           <cell r="T20" t="str">
             <v>解</v>
           </cell>
+          <cell r="U20"/>
         </row>
         <row r="21">
           <cell r="R21" t="str">
             <v>马</v>
           </cell>
+          <cell r="S21"/>
           <cell r="T21" t="str">
             <v>坚</v>
           </cell>
@@ -4438,6 +4485,7 @@
           <cell r="R22" t="str">
             <v>马</v>
           </cell>
+          <cell r="S22"/>
           <cell r="T22" t="str">
             <v>奋</v>
           </cell>
@@ -4446,6 +4494,7 @@
           <cell r="R23" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S23"/>
           <cell r="T23" t="str">
             <v>连</v>
           </cell>
@@ -4454,30 +4503,37 @@
           <cell r="R24" t="str">
             <v>士</v>
           </cell>
+          <cell r="S24"/>
           <cell r="T24" t="str">
             <v>敏</v>
           </cell>
+          <cell r="U24"/>
         </row>
         <row r="25">
           <cell r="R25" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S25"/>
           <cell r="T25" t="str">
             <v>透</v>
           </cell>
+          <cell r="U25"/>
         </row>
         <row r="26">
           <cell r="R26" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S26"/>
           <cell r="T26" t="str">
             <v>藤</v>
           </cell>
+          <cell r="U26"/>
         </row>
         <row r="27">
           <cell r="R27" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S27"/>
           <cell r="T27" t="str">
             <v>锁</v>
           </cell>
@@ -4489,6 +4545,7 @@
           <cell r="R28" t="str">
             <v>士</v>
           </cell>
+          <cell r="S28"/>
           <cell r="T28" t="str">
             <v>实</v>
           </cell>
@@ -4497,6 +4554,7 @@
           <cell r="R29" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S29"/>
           <cell r="T29" t="str">
             <v>乱</v>
           </cell>
@@ -4505,16 +4563,21 @@
           <cell r="R30" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S30"/>
+          <cell r="T30"/>
         </row>
         <row r="31">
           <cell r="R31" t="str">
             <v>弩</v>
           </cell>
+          <cell r="S31"/>
+          <cell r="T31"/>
         </row>
         <row r="32">
           <cell r="R32" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S32"/>
           <cell r="T32" t="str">
             <v>破</v>
           </cell>
@@ -4523,43 +4586,55 @@
           <cell r="R33" t="str">
             <v>相</v>
           </cell>
+          <cell r="S33"/>
+          <cell r="T33"/>
+          <cell r="U33"/>
         </row>
         <row r="34">
           <cell r="R34" t="str">
             <v>鼓</v>
           </cell>
+          <cell r="S34"/>
           <cell r="T34" t="str">
             <v>白</v>
           </cell>
+          <cell r="U34"/>
         </row>
         <row r="35">
           <cell r="R35" t="str">
             <v>相</v>
           </cell>
+          <cell r="S35"/>
           <cell r="T35" t="str">
             <v>励</v>
           </cell>
+          <cell r="U35"/>
         </row>
         <row r="36">
           <cell r="R36" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S36"/>
           <cell r="T36" t="str">
             <v>百</v>
           </cell>
+          <cell r="U36"/>
         </row>
         <row r="37">
           <cell r="R37" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S37"/>
           <cell r="T37" t="str">
             <v>米</v>
           </cell>
+          <cell r="U37"/>
         </row>
         <row r="38">
           <cell r="R38" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S38"/>
           <cell r="T38" t="str">
             <v>伏</v>
           </cell>
@@ -4571,43 +4646,55 @@
           <cell r="R39" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S39"/>
           <cell r="T39" t="str">
             <v>境</v>
           </cell>
+          <cell r="U39"/>
         </row>
         <row r="40">
           <cell r="R40" t="str">
             <v>鼓</v>
           </cell>
+          <cell r="S40"/>
           <cell r="T40" t="str">
             <v>陷</v>
           </cell>
+          <cell r="U40"/>
         </row>
         <row r="41">
           <cell r="R41" t="str">
             <v>相</v>
           </cell>
+          <cell r="S41"/>
           <cell r="T41" t="str">
             <v>静</v>
           </cell>
+          <cell r="U41"/>
         </row>
         <row r="42">
           <cell r="R42" t="str">
             <v>炮</v>
           </cell>
+          <cell r="S42"/>
+          <cell r="T42"/>
+          <cell r="U42"/>
         </row>
         <row r="43">
           <cell r="R43" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S43"/>
           <cell r="T43" t="str">
             <v>溃</v>
           </cell>
+          <cell r="U43"/>
         </row>
         <row r="44">
           <cell r="R44" t="str">
             <v>鼓</v>
           </cell>
+          <cell r="S44"/>
           <cell r="T44" t="str">
             <v>碉</v>
           </cell>
@@ -4616,123 +4703,155 @@
           <cell r="R45" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S45"/>
           <cell r="T45" t="str">
             <v>藤</v>
           </cell>
+          <cell r="U45"/>
         </row>
         <row r="46">
           <cell r="R46" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S46"/>
           <cell r="T46" t="str">
             <v>缓</v>
           </cell>
+          <cell r="U46"/>
         </row>
         <row r="47">
           <cell r="R47" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S47"/>
           <cell r="T47" t="str">
             <v>乱</v>
           </cell>
+          <cell r="U47"/>
         </row>
         <row r="48">
           <cell r="R48" t="str">
             <v>弩</v>
           </cell>
+          <cell r="S48"/>
+          <cell r="T48"/>
+          <cell r="U48"/>
         </row>
         <row r="49">
           <cell r="R49" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S49"/>
           <cell r="T49" t="str">
             <v>境</v>
           </cell>
+          <cell r="U49"/>
         </row>
         <row r="50">
           <cell r="R50" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S50"/>
           <cell r="T50" t="str">
             <v>纷</v>
           </cell>
+          <cell r="U50"/>
         </row>
         <row r="51">
           <cell r="R51" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S51"/>
           <cell r="T51" t="str">
             <v>天</v>
           </cell>
+          <cell r="U51"/>
         </row>
         <row r="52">
           <cell r="R52" t="str">
             <v>车</v>
           </cell>
+          <cell r="S52"/>
           <cell r="T52" t="str">
             <v>青</v>
           </cell>
+          <cell r="U52"/>
         </row>
         <row r="53">
           <cell r="R53" t="str">
             <v>相</v>
           </cell>
+          <cell r="S53"/>
           <cell r="T53" t="str">
             <v>国</v>
           </cell>
+          <cell r="U53"/>
         </row>
         <row r="54">
           <cell r="R54" t="str">
             <v>马</v>
           </cell>
+          <cell r="S54"/>
           <cell r="T54" t="str">
             <v>旋</v>
           </cell>
+          <cell r="U54"/>
         </row>
         <row r="55">
           <cell r="R55" t="str">
             <v>士</v>
           </cell>
+          <cell r="S55"/>
           <cell r="T55" t="str">
             <v>斧</v>
           </cell>
+          <cell r="U55"/>
         </row>
         <row r="56">
           <cell r="R56" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S56"/>
           <cell r="T56" t="str">
             <v>雨</v>
           </cell>
+          <cell r="U56"/>
         </row>
         <row r="57">
           <cell r="R57" t="str">
             <v>士</v>
           </cell>
+          <cell r="S57"/>
           <cell r="T57" t="str">
             <v>护</v>
           </cell>
+          <cell r="U57"/>
         </row>
         <row r="58">
           <cell r="R58" t="str">
             <v>车</v>
           </cell>
+          <cell r="S58"/>
           <cell r="T58" t="str">
             <v>分</v>
           </cell>
+          <cell r="U58"/>
         </row>
         <row r="59">
           <cell r="R59" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S59"/>
           <cell r="T59" t="str">
             <v>连</v>
           </cell>
+          <cell r="U59"/>
         </row>
         <row r="60">
           <cell r="R60" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S60"/>
           <cell r="T60" t="str">
             <v>百</v>
           </cell>
@@ -4744,6 +4863,7 @@
           <cell r="R61" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S61"/>
           <cell r="T61" t="str">
             <v>青</v>
           </cell>
@@ -4755,38 +4875,47 @@
           <cell r="R62" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S62"/>
           <cell r="T62" t="str">
             <v>青</v>
           </cell>
+          <cell r="U62"/>
         </row>
         <row r="63">
           <cell r="R63" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S63"/>
           <cell r="T63" t="str">
             <v>商</v>
           </cell>
+          <cell r="U63"/>
         </row>
         <row r="64">
           <cell r="R64" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S64"/>
           <cell r="T64" t="str">
             <v>坚</v>
           </cell>
+          <cell r="U64"/>
         </row>
         <row r="65">
           <cell r="R65" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S65"/>
           <cell r="T65" t="str">
             <v>奋</v>
           </cell>
+          <cell r="U65"/>
         </row>
         <row r="66">
           <cell r="R66" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S66"/>
           <cell r="T66" t="str">
             <v>透</v>
           </cell>
@@ -4798,43 +4927,55 @@
           <cell r="R67" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S67"/>
+          <cell r="T67"/>
+          <cell r="U67"/>
         </row>
         <row r="68">
           <cell r="R68" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S68"/>
           <cell r="T68" t="str">
             <v>鬼</v>
           </cell>
+          <cell r="U68"/>
         </row>
         <row r="69">
           <cell r="R69" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S69"/>
           <cell r="T69" t="str">
             <v>连</v>
           </cell>
+          <cell r="U69"/>
         </row>
         <row r="70">
           <cell r="R70" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S70"/>
           <cell r="T70" t="str">
             <v>坚</v>
           </cell>
+          <cell r="U70"/>
         </row>
         <row r="71">
           <cell r="R71" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S71"/>
           <cell r="T71" t="str">
             <v>透</v>
           </cell>
+          <cell r="U71"/>
         </row>
         <row r="72">
           <cell r="R72" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S72"/>
           <cell r="T72" t="str">
             <v>识</v>
           </cell>
@@ -4846,6 +4987,7 @@
           <cell r="R73" t="str">
             <v>相</v>
           </cell>
+          <cell r="S73"/>
           <cell r="T73" t="str">
             <v>虐</v>
           </cell>
@@ -4854,6 +4996,7 @@
           <cell r="R74" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S74"/>
           <cell r="T74" t="str">
             <v>伏</v>
           </cell>
@@ -4862,6 +5005,7 @@
           <cell r="R75" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S75"/>
           <cell r="T75" t="str">
             <v>速</v>
           </cell>
@@ -4870,6 +5014,7 @@
           <cell r="R76" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S76"/>
           <cell r="T76" t="str">
             <v>境</v>
           </cell>
@@ -4878,6 +5023,7 @@
           <cell r="R77" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S77"/>
           <cell r="T77" t="str">
             <v>励</v>
           </cell>
@@ -4889,6 +5035,7 @@
           <cell r="R78" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S78"/>
           <cell r="T78" t="str">
             <v>伏</v>
           </cell>
@@ -4900,93 +5047,119 @@
           <cell r="R79" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S79"/>
           <cell r="T79" t="str">
             <v>敏</v>
           </cell>
+          <cell r="U79"/>
         </row>
         <row r="80">
           <cell r="R80" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S80"/>
           <cell r="T80" t="str">
             <v>虐</v>
           </cell>
+          <cell r="U80"/>
         </row>
         <row r="81">
           <cell r="R81" t="str">
             <v>炮</v>
           </cell>
+          <cell r="S81"/>
+          <cell r="T81"/>
+          <cell r="U81"/>
         </row>
         <row r="82">
           <cell r="R82" t="str">
             <v>炮</v>
           </cell>
+          <cell r="S82"/>
         </row>
         <row r="83">
           <cell r="R83" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S83"/>
           <cell r="T83" t="str">
             <v>青</v>
           </cell>
+          <cell r="U83"/>
         </row>
         <row r="84">
           <cell r="R84" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S84"/>
           <cell r="T84" t="str">
             <v>劫</v>
           </cell>
+          <cell r="U84"/>
         </row>
         <row r="85">
           <cell r="R85" t="str">
             <v>士</v>
           </cell>
+          <cell r="S85"/>
+          <cell r="T85"/>
+          <cell r="U85"/>
         </row>
         <row r="86">
           <cell r="R86" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S86"/>
           <cell r="T86" t="str">
             <v>敏</v>
           </cell>
+          <cell r="U86"/>
         </row>
         <row r="87">
           <cell r="R87" t="str">
             <v>相</v>
           </cell>
+          <cell r="S87"/>
           <cell r="T87" t="str">
             <v>米</v>
           </cell>
+          <cell r="U87"/>
         </row>
         <row r="88">
           <cell r="R88" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S88"/>
           <cell r="T88" t="str">
             <v>连</v>
           </cell>
+          <cell r="U88"/>
         </row>
         <row r="89">
           <cell r="R89" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S89"/>
           <cell r="T89" t="str">
             <v>米</v>
           </cell>
+          <cell r="U89"/>
         </row>
         <row r="90">
           <cell r="R90" t="str">
             <v>鼓</v>
           </cell>
+          <cell r="S90"/>
           <cell r="T90" t="str">
             <v>米</v>
           </cell>
+          <cell r="U90"/>
         </row>
         <row r="91">
           <cell r="R91" t="str">
             <v>鼓</v>
           </cell>
+          <cell r="S91"/>
           <cell r="T91" t="str">
             <v>白</v>
           </cell>
@@ -4995,6 +5168,7 @@
           <cell r="R92" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S92"/>
           <cell r="T92" t="str">
             <v>陷</v>
           </cell>
@@ -5003,54 +5177,67 @@
           <cell r="R93" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S93"/>
           <cell r="T93" t="str">
             <v>旋</v>
           </cell>
+          <cell r="U93"/>
         </row>
         <row r="94">
           <cell r="R94" t="str">
             <v>车</v>
           </cell>
+          <cell r="S94"/>
           <cell r="T94" t="str">
             <v>虎</v>
           </cell>
+          <cell r="U94"/>
         </row>
         <row r="95">
           <cell r="R95" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S95"/>
           <cell r="T95" t="str">
             <v>连</v>
           </cell>
+          <cell r="U95"/>
         </row>
         <row r="96">
           <cell r="R96" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S96"/>
           <cell r="T96" t="str">
             <v>雨</v>
           </cell>
+          <cell r="U96"/>
         </row>
         <row r="97">
           <cell r="R97" t="str">
             <v>士</v>
           </cell>
+          <cell r="S97"/>
           <cell r="T97" t="str">
             <v>奋</v>
           </cell>
+          <cell r="U97"/>
         </row>
         <row r="98">
           <cell r="R98" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S98"/>
           <cell r="T98" t="str">
             <v>连</v>
           </cell>
+          <cell r="U98"/>
         </row>
         <row r="99">
           <cell r="R99" t="str">
             <v>相</v>
           </cell>
+          <cell r="S99"/>
           <cell r="T99" t="str">
             <v>商</v>
           </cell>
@@ -5062,6 +5249,7 @@
           <cell r="R100" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S100"/>
           <cell r="T100" t="str">
             <v>炎</v>
           </cell>
@@ -5073,11 +5261,15 @@
           <cell r="R101" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S101"/>
+          <cell r="T101"/>
+          <cell r="U101"/>
         </row>
         <row r="102">
           <cell r="R102" t="str">
             <v>马</v>
           </cell>
+          <cell r="S102"/>
           <cell r="T102" t="str">
             <v>学</v>
           </cell>
@@ -5089,32 +5281,43 @@
           <cell r="R103" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S103"/>
           <cell r="T103" t="str">
             <v>炎</v>
           </cell>
+          <cell r="U103"/>
         </row>
         <row r="104">
           <cell r="R104" t="str">
             <v>相</v>
           </cell>
+          <cell r="S104"/>
+          <cell r="T104"/>
+          <cell r="U104"/>
         </row>
         <row r="105">
           <cell r="R105" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S105"/>
           <cell r="T105" t="str">
             <v>励</v>
           </cell>
+          <cell r="U105"/>
         </row>
         <row r="106">
           <cell r="R106" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S106"/>
+          <cell r="T106"/>
+          <cell r="U106"/>
         </row>
         <row r="107">
           <cell r="R107" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S107"/>
           <cell r="T107" t="str">
             <v>伏</v>
           </cell>
@@ -5126,6 +5329,7 @@
           <cell r="R108" t="str">
             <v>乐</v>
           </cell>
+          <cell r="S108"/>
           <cell r="T108" t="str">
             <v>碉</v>
           </cell>
@@ -5137,6 +5341,7 @@
           <cell r="R109" t="str">
             <v>乐</v>
           </cell>
+          <cell r="S109"/>
           <cell r="T109" t="str">
             <v>曲</v>
           </cell>
@@ -5148,11 +5353,15 @@
           <cell r="R110" t="str">
             <v>炮</v>
           </cell>
+          <cell r="S110"/>
+          <cell r="T110"/>
+          <cell r="U110"/>
         </row>
         <row r="111">
           <cell r="R111" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S111"/>
           <cell r="T111" t="str">
             <v>透</v>
           </cell>
@@ -5161,6 +5370,7 @@
           <cell r="R112" t="str">
             <v>弩</v>
           </cell>
+          <cell r="S112"/>
           <cell r="T112" t="str">
             <v>虐</v>
           </cell>
@@ -5169,6 +5379,7 @@
           <cell r="R113" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S113"/>
           <cell r="T113" t="str">
             <v>刺</v>
           </cell>
@@ -5180,22 +5391,27 @@
           <cell r="R114" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S114"/>
           <cell r="T114" t="str">
             <v>敏</v>
           </cell>
+          <cell r="U114"/>
         </row>
         <row r="115">
           <cell r="R115" t="str">
             <v>士</v>
           </cell>
+          <cell r="S115"/>
           <cell r="T115" t="str">
             <v>乱</v>
           </cell>
+          <cell r="U115"/>
         </row>
         <row r="116">
           <cell r="R116" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S116"/>
           <cell r="T116" t="str">
             <v>实</v>
           </cell>
@@ -5207,118 +5423,147 @@
           <cell r="R117" t="str">
             <v>相</v>
           </cell>
+          <cell r="S117"/>
           <cell r="T117" t="str">
             <v>励</v>
           </cell>
+          <cell r="U117"/>
         </row>
         <row r="118">
           <cell r="R118" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S118"/>
           <cell r="T118" t="str">
             <v>连</v>
           </cell>
+          <cell r="U118"/>
         </row>
         <row r="119">
           <cell r="R119" t="str">
             <v>鼓</v>
           </cell>
+          <cell r="S119"/>
           <cell r="T119" t="str">
             <v>励</v>
           </cell>
+          <cell r="U119"/>
         </row>
         <row r="120">
           <cell r="R120" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S120"/>
           <cell r="T120" t="str">
             <v>炽</v>
           </cell>
+          <cell r="U120"/>
         </row>
         <row r="121">
           <cell r="R121" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S121"/>
           <cell r="T121" t="str">
             <v>奋</v>
           </cell>
+          <cell r="U121"/>
         </row>
         <row r="122">
           <cell r="R122" t="str">
             <v>弩</v>
           </cell>
+          <cell r="S122"/>
           <cell r="T122" t="str">
             <v>透</v>
           </cell>
+          <cell r="U122"/>
         </row>
         <row r="123">
           <cell r="R123" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S123"/>
           <cell r="T123" t="str">
             <v>缓</v>
           </cell>
+          <cell r="U123"/>
         </row>
         <row r="124">
           <cell r="R124" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S124"/>
           <cell r="T124" t="str">
             <v>复</v>
           </cell>
+          <cell r="U124"/>
         </row>
         <row r="125">
           <cell r="R125" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S125"/>
           <cell r="T125" t="str">
             <v>实</v>
           </cell>
+          <cell r="U125"/>
         </row>
         <row r="126">
           <cell r="R126" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S126"/>
           <cell r="T126" t="str">
             <v>劫</v>
           </cell>
+          <cell r="U126"/>
         </row>
         <row r="127">
           <cell r="R127" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S127"/>
           <cell r="T127" t="str">
             <v>竟</v>
           </cell>
+          <cell r="U127"/>
         </row>
         <row r="128">
           <cell r="R128" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S128"/>
           <cell r="T128" t="str">
             <v>破</v>
           </cell>
+          <cell r="U128"/>
         </row>
         <row r="129">
           <cell r="R129" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S129"/>
           <cell r="T129" t="str">
             <v>竟</v>
           </cell>
+          <cell r="U129"/>
         </row>
         <row r="130">
           <cell r="R130" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S130"/>
           <cell r="T130" t="str">
             <v>虐</v>
           </cell>
+          <cell r="U130"/>
         </row>
         <row r="131">
           <cell r="R131" t="str">
             <v>车</v>
           </cell>
+          <cell r="S131"/>
           <cell r="T131" t="str">
             <v>魔</v>
           </cell>
@@ -5330,59 +5575,75 @@
           <cell r="R132" t="str">
             <v>车</v>
           </cell>
+          <cell r="S132"/>
           <cell r="T132" t="str">
             <v>纷</v>
           </cell>
+          <cell r="U132"/>
         </row>
         <row r="133">
           <cell r="R133" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S133"/>
           <cell r="T133" t="str">
             <v>延</v>
           </cell>
+          <cell r="U133"/>
         </row>
         <row r="134">
           <cell r="R134" t="str">
             <v>乐</v>
           </cell>
+          <cell r="S134"/>
           <cell r="T134" t="str">
             <v>曲</v>
           </cell>
+          <cell r="U134"/>
         </row>
         <row r="135">
           <cell r="R135" t="str">
             <v>马</v>
           </cell>
+          <cell r="S135"/>
           <cell r="T135" t="str">
             <v>虐</v>
           </cell>
+          <cell r="U135"/>
         </row>
         <row r="136">
           <cell r="R136" t="str">
             <v>炮</v>
           </cell>
+          <cell r="S136"/>
+          <cell r="T136"/>
+          <cell r="U136"/>
         </row>
         <row r="137">
           <cell r="R137" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S137"/>
           <cell r="T137" t="str">
             <v>火</v>
           </cell>
+          <cell r="U137"/>
         </row>
         <row r="138">
           <cell r="R138" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S138"/>
           <cell r="T138" t="str">
             <v>劫</v>
           </cell>
+          <cell r="U138"/>
         </row>
         <row r="139">
           <cell r="R139" t="str">
             <v>刀</v>
           </cell>
+          <cell r="S139"/>
           <cell r="T139" t="str">
             <v>劫</v>
           </cell>
@@ -5391,6 +5652,7 @@
           <cell r="R140" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S140"/>
           <cell r="T140" t="str">
             <v>励</v>
           </cell>
@@ -5402,6 +5664,7 @@
           <cell r="R141" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S141"/>
           <cell r="T141" t="str">
             <v>奇</v>
           </cell>
@@ -5410,11 +5673,13 @@
           <cell r="R142" t="str">
             <v>相</v>
           </cell>
+          <cell r="S142"/>
         </row>
         <row r="143">
           <cell r="R143" t="str">
             <v>相</v>
           </cell>
+          <cell r="S143"/>
           <cell r="T143" t="str">
             <v>溃</v>
           </cell>
@@ -5423,6 +5688,7 @@
           <cell r="R144" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S144"/>
           <cell r="T144" t="str">
             <v>敏</v>
           </cell>
@@ -5431,6 +5697,7 @@
           <cell r="R145" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S145"/>
           <cell r="T145" t="str">
             <v>缓</v>
           </cell>
@@ -5439,6 +5706,7 @@
           <cell r="R146" t="str">
             <v>士</v>
           </cell>
+          <cell r="S146"/>
           <cell r="T146" t="str">
             <v>虐</v>
           </cell>
@@ -5447,6 +5715,7 @@
           <cell r="R147" t="str">
             <v>相</v>
           </cell>
+          <cell r="S147"/>
           <cell r="T147" t="str">
             <v>米</v>
           </cell>
@@ -5455,6 +5724,7 @@
           <cell r="R148" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S148"/>
           <cell r="T148" t="str">
             <v>敏</v>
           </cell>
@@ -5463,6 +5733,7 @@
           <cell r="R149" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S149"/>
           <cell r="T149" t="str">
             <v>缓</v>
           </cell>
@@ -5471,56 +5742,73 @@
           <cell r="R150" t="str">
             <v>车</v>
           </cell>
+          <cell r="S150"/>
           <cell r="T150" t="str">
             <v>破</v>
           </cell>
+          <cell r="U150"/>
         </row>
         <row r="151">
           <cell r="R151" t="str">
             <v>车</v>
           </cell>
+          <cell r="S151"/>
           <cell r="T151" t="str">
             <v>刺</v>
           </cell>
+          <cell r="U151"/>
         </row>
         <row r="152">
           <cell r="R152" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S152"/>
           <cell r="T152" t="str">
             <v>雷</v>
           </cell>
+          <cell r="U152"/>
         </row>
         <row r="153">
           <cell r="R153" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S153"/>
+          <cell r="T153"/>
+          <cell r="U153"/>
         </row>
         <row r="154">
           <cell r="R154" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S154"/>
           <cell r="T154" t="str">
             <v>火</v>
           </cell>
+          <cell r="U154"/>
         </row>
         <row r="155">
           <cell r="R155" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S155"/>
+          <cell r="T155"/>
+          <cell r="U155"/>
         </row>
         <row r="156">
           <cell r="R156" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S156"/>
           <cell r="T156" t="str">
             <v>静</v>
           </cell>
+          <cell r="U156"/>
         </row>
         <row r="157">
           <cell r="R157" t="str">
             <v>扇</v>
           </cell>
+          <cell r="S157"/>
           <cell r="T157" t="str">
             <v>励</v>
           </cell>
@@ -5532,51 +5820,65 @@
           <cell r="R158" t="str">
             <v>马</v>
           </cell>
+          <cell r="S158"/>
           <cell r="T158" t="str">
             <v>乱</v>
           </cell>
+          <cell r="U158"/>
         </row>
         <row r="159">
           <cell r="R159" t="str">
             <v>弓</v>
           </cell>
+          <cell r="S159"/>
           <cell r="T159" t="str">
             <v>复</v>
           </cell>
+          <cell r="U159"/>
         </row>
         <row r="160">
           <cell r="R160" t="str">
             <v>医</v>
           </cell>
+          <cell r="S160"/>
           <cell r="T160" t="str">
             <v>药</v>
           </cell>
+          <cell r="U160"/>
         </row>
         <row r="161">
           <cell r="R161" t="str">
             <v>戟</v>
           </cell>
+          <cell r="S161"/>
+          <cell r="T161"/>
+          <cell r="U161"/>
         </row>
         <row r="162">
           <cell r="R162" t="str">
             <v>马</v>
           </cell>
+          <cell r="S162"/>
           <cell r="T162" t="str">
             <v>羽</v>
           </cell>
+          <cell r="U162"/>
         </row>
         <row r="163">
           <cell r="R163" t="str">
             <v>医</v>
           </cell>
+          <cell r="S163"/>
           <cell r="T163" t="str">
             <v>调</v>
           </cell>
+          <cell r="U163"/>
         </row>
         <row r="164">
           <cell r="R164" t="str">
             <v>谋</v>
           </cell>
+          <cell r="S164"/>
           <cell r="T164" t="str">
             <v>天</v>
           </cell>
@@ -5588,35 +5890,47 @@
           <cell r="R165" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S165"/>
           <cell r="T165" t="str">
             <v>劫</v>
           </cell>
+          <cell r="U165"/>
         </row>
         <row r="166">
           <cell r="R166" t="str">
             <v>炮</v>
           </cell>
+          <cell r="S166"/>
+          <cell r="T166"/>
+          <cell r="U166"/>
         </row>
         <row r="167">
           <cell r="R167" t="str">
             <v>马</v>
           </cell>
+          <cell r="S167"/>
           <cell r="T167" t="str">
             <v>乱</v>
           </cell>
+          <cell r="U167"/>
         </row>
         <row r="168">
           <cell r="R168" t="str">
             <v>枪</v>
           </cell>
+          <cell r="S168"/>
+          <cell r="T168"/>
+          <cell r="U168"/>
         </row>
         <row r="169">
           <cell r="R169" t="str">
             <v>乐</v>
           </cell>
+          <cell r="S169"/>
           <cell r="T169" t="str">
             <v>碉</v>
           </cell>
+          <cell r="U169"/>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -5887,7 +6201,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AR84"/>
+  <dimension ref="A1:AT84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -5914,13 +6228,13 @@
     <col min="30" max="31" width="5.75" customWidth="1"/>
     <col min="32" max="35" width="5.5" customWidth="1"/>
     <col min="36" max="36" width="4.625" customWidth="1"/>
-    <col min="37" max="38" width="12.5" customWidth="1"/>
-    <col min="39" max="39" width="19.625" customWidth="1"/>
-    <col min="40" max="40" width="6.5" customWidth="1"/>
-    <col min="41" max="41" width="5.875" customWidth="1"/>
+    <col min="37" max="40" width="12.5" customWidth="1"/>
+    <col min="41" max="41" width="19.625" customWidth="1"/>
+    <col min="42" max="42" width="6.5" customWidth="1"/>
+    <col min="43" max="43" width="5.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="57" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:46" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5928,16 +6242,16 @@
         <v>13</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>9</v>
@@ -5949,16 +6263,16 @@
         <v>22</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>75</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>34</v>
@@ -5967,25 +6281,25 @@
         <v>121</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>97</v>
       </c>
       <c r="R1" s="19" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="S1" s="19" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="T1" s="19" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="U1" s="19" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="V1" s="19" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="W1" s="7" t="s">
         <v>141</v>
@@ -5994,61 +6308,67 @@
         <v>145</v>
       </c>
       <c r="Y1" s="21" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="Z1" s="21" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="AA1" s="21" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="AC1" s="7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AD1" s="7" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="AE1" s="23" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="AF1" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="AG1" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="AH1" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="AI1" s="23" t="s">
         <v>476</v>
       </c>
-      <c r="AG1" s="23" t="s">
+      <c r="AJ1" s="23" t="s">
         <v>477</v>
-      </c>
-      <c r="AH1" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="AI1" s="23" t="s">
-        <v>479</v>
-      </c>
-      <c r="AJ1" s="23" t="s">
-        <v>480</v>
       </c>
       <c r="AK1" s="7" t="s">
         <v>28</v>
       </c>
       <c r="AL1" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="AM1" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="AN1" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="AO1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AN1" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="AO1" s="6" t="s">
+      <c r="AP1" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AQ1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -6056,16 +6376,16 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6077,16 +6397,16 @@
         <v>26</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>35</v>
@@ -6095,25 +6415,25 @@
         <v>122</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="R2" s="20" t="s">
         <v>102</v>
       </c>
       <c r="S2" s="20" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="T2" s="20" t="s">
+        <v>539</v>
+      </c>
+      <c r="U2" s="20" t="s">
         <v>542</v>
       </c>
-      <c r="U2" s="20" t="s">
-        <v>545</v>
-      </c>
       <c r="V2" s="20" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="W2" s="3" t="s">
         <v>144</v>
@@ -6122,31 +6442,31 @@
         <v>147</v>
       </c>
       <c r="Y2" s="22" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Z2" s="22" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AA2" s="22" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AD2" s="3" t="s">
         <v>32</v>
       </c>
       <c r="AE2" s="24" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="AF2" s="24" t="s">
         <v>131</v>
       </c>
       <c r="AG2" s="24" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AH2" s="24" t="s">
         <v>133</v>
@@ -6155,28 +6475,34 @@
         <v>134</v>
       </c>
       <c r="AJ2" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="AL2" s="51" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="AM2" s="51" t="s">
-        <v>245</v>
+        <v>636</v>
       </c>
       <c r="AN2" s="51" t="s">
-        <v>214</v>
+        <v>637</v>
       </c>
       <c r="AO2" s="51" t="s">
+        <v>638</v>
+      </c>
+      <c r="AP2" s="51" t="s">
+        <v>213</v>
+      </c>
+      <c r="AQ2" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="AP2" s="4" t="s">
+      <c r="AR2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>41</v>
       </c>
@@ -6184,16 +6510,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>11</v>
@@ -6205,16 +6531,16 @@
         <v>24</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>76</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>36</v>
@@ -6223,7 +6549,7 @@
         <v>123</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>98</v>
@@ -6232,10 +6558,10 @@
         <v>24</v>
       </c>
       <c r="S3" s="20" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="T3" s="20" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="U3" s="20" t="s">
         <v>24</v>
@@ -6250,19 +6576,19 @@
         <v>146</v>
       </c>
       <c r="Y3" s="22" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="Z3" s="22" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AA3" s="22" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AD3" s="3" t="s">
         <v>84</v>
@@ -6274,7 +6600,7 @@
         <v>132</v>
       </c>
       <c r="AG3" s="24" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AH3" s="24" t="s">
         <v>84</v>
@@ -6283,28 +6609,34 @@
         <v>86</v>
       </c>
       <c r="AJ3" s="24" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AL3" s="51" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="AM3" s="51" t="s">
+        <v>633</v>
+      </c>
+      <c r="AN3" s="51" t="s">
+        <v>633</v>
+      </c>
+      <c r="AO3" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="AN3" s="51" t="s">
-        <v>216</v>
-      </c>
-      <c r="AO3" s="51" t="s">
+      <c r="AP3" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="AQ3" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="AP3" s="4" t="s">
+      <c r="AR3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -6312,16 +6644,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>53</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>12</v>
@@ -6333,16 +6665,16 @@
         <v>20</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>77</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>37</v>
@@ -6351,7 +6683,7 @@
         <v>124</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>99</v>
@@ -6363,7 +6695,7 @@
         <v>12</v>
       </c>
       <c r="T4" s="20" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="U4" s="20" t="s">
         <v>33</v>
@@ -6378,19 +6710,19 @@
         <v>143</v>
       </c>
       <c r="Y4" s="22" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="Z4" s="22" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AA4" s="22" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="AB4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AD4" s="3" t="s">
         <v>7</v>
@@ -6402,7 +6734,7 @@
         <v>7</v>
       </c>
       <c r="AG4" s="24" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AH4" s="24" t="s">
         <v>85</v>
@@ -6411,43 +6743,49 @@
         <v>85</v>
       </c>
       <c r="AJ4" s="24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AK4" s="3" t="s">
         <v>20</v>
       </c>
       <c r="AL4" s="51" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="AM4" s="51" t="s">
+        <v>634</v>
+      </c>
+      <c r="AN4" s="51" t="s">
+        <v>634</v>
+      </c>
+      <c r="AO4" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="AN4" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="AO4" s="51" t="s">
+      <c r="AP4" s="51" t="s">
+        <v>216</v>
+      </c>
+      <c r="AQ4" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="AP4" s="4" t="s">
+      <c r="AR4" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>200001</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -6488,41 +6826,43 @@
       <c r="AI5" s="44"/>
       <c r="AJ5" s="44"/>
       <c r="AK5" s="5" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="AL5" s="52"/>
       <c r="AM5" s="52"/>
       <c r="AN5" s="52"/>
-      <c r="AO5" s="5">
+      <c r="AO5" s="52"/>
+      <c r="AP5" s="52"/>
+      <c r="AQ5" s="5">
         <v>4</v>
       </c>
-      <c r="AP5" t="s">
+      <c r="AR5" t="s">
         <v>44</v>
       </c>
-      <c r="AQ5">
+      <c r="AS5" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C5)</f>
-        <v>6</v>
-      </c>
-      <c r="AR5" s="5" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AT5" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>200002</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -6532,7 +6872,7 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
@@ -6565,41 +6905,43 @@
       <c r="AI6" s="44"/>
       <c r="AJ6" s="44"/>
       <c r="AK6" s="5" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AL6" s="52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM6" s="52"/>
       <c r="AN6" s="52"/>
-      <c r="AO6" s="5">
+      <c r="AO6" s="52"/>
+      <c r="AP6" s="52"/>
+      <c r="AQ6" s="5">
         <v>2</v>
       </c>
-      <c r="AP6" t="s">
-        <v>179</v>
-      </c>
-      <c r="AQ6">
+      <c r="AR6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AS6" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C6)</f>
-        <v>11</v>
-      </c>
-      <c r="AR6" s="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AT6" s="5"/>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>200003</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G7" s="5">
         <v>1</v>
@@ -6642,27 +6984,29 @@
       <c r="AI7" s="44"/>
       <c r="AJ7" s="44"/>
       <c r="AK7" s="5" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="AL7" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM7" s="52" t="s">
-        <v>241</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="AM7" s="52"/>
       <c r="AN7" s="52"/>
-      <c r="AO7" s="5">
+      <c r="AO7" s="52" t="s">
+        <v>239</v>
+      </c>
+      <c r="AP7" s="52"/>
+      <c r="AQ7" s="5">
         <v>1</v>
       </c>
-      <c r="AP7" t="s">
-        <v>168</v>
-      </c>
-      <c r="AQ7">
+      <c r="AR7" t="s">
+        <v>167</v>
+      </c>
+      <c r="AS7" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C7)</f>
-        <v>11</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>200004</v>
       </c>
@@ -6670,14 +7014,14 @@
         <v>138</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
         <v>74</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -6727,25 +7071,27 @@
         <v>110</v>
       </c>
       <c r="AL8" s="52" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AM8" s="52"/>
       <c r="AN8" s="52"/>
-      <c r="AO8" s="5">
+      <c r="AO8" s="52"/>
+      <c r="AP8" s="52"/>
+      <c r="AQ8" s="5">
         <v>3</v>
       </c>
-      <c r="AP8" s="55" t="s">
+      <c r="AR8" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="AQ8">
+      <c r="AS8" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C8)</f>
-        <v>8</v>
-      </c>
-      <c r="AR8" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AT8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>200005</v>
       </c>
@@ -6753,14 +7099,14 @@
         <v>55</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G9" s="5">
         <v>1</v>
@@ -6807,43 +7153,45 @@
       <c r="AI9" s="44"/>
       <c r="AJ9" s="44"/>
       <c r="AK9" s="5" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="AL9" s="52"/>
-      <c r="AM9" s="52" t="s">
+      <c r="AM9" s="52"/>
+      <c r="AN9" s="52"/>
+      <c r="AO9" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="AN9" s="52"/>
-      <c r="AO9" s="5">
+      <c r="AP9" s="52"/>
+      <c r="AQ9" s="5">
         <v>2</v>
       </c>
-      <c r="AP9" s="55" t="s">
+      <c r="AR9" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="AQ9">
+      <c r="AS9" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C9)</f>
-        <v>10</v>
-      </c>
-      <c r="AR9" s="5" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AT9" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>200006</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="5" t="s">
         <v>107</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G10" s="5">
         <v>1</v>
@@ -6884,43 +7232,45 @@
       <c r="AI10" s="44"/>
       <c r="AJ10" s="44"/>
       <c r="AK10" s="5" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="AL10" s="52"/>
-      <c r="AM10" s="52" t="s">
+      <c r="AM10" s="52"/>
+      <c r="AN10" s="52"/>
+      <c r="AO10" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="AN10" s="52"/>
-      <c r="AO10" s="5">
+      <c r="AP10" s="52"/>
+      <c r="AQ10" s="5">
         <v>2</v>
       </c>
-      <c r="AP10" s="55" t="s">
+      <c r="AR10" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="AQ10">
+      <c r="AS10" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C10)</f>
-        <v>12</v>
-      </c>
-      <c r="AR10" s="5" t="s">
+        <v>#VALUE!</v>
+      </c>
+      <c r="AT10" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>200007</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G11" s="5">
         <v>1</v>
@@ -6966,33 +7316,35 @@
       <c r="AL11" s="52"/>
       <c r="AM11" s="52"/>
       <c r="AN11" s="52"/>
-      <c r="AO11" s="5">
+      <c r="AO11" s="52"/>
+      <c r="AP11" s="52"/>
+      <c r="AQ11" s="5">
         <v>2</v>
       </c>
-      <c r="AP11" s="55" t="s">
-        <v>161</v>
-      </c>
-      <c r="AQ11">
+      <c r="AR11" s="55" t="s">
+        <v>160</v>
+      </c>
+      <c r="AS11" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C11)</f>
-        <v>13</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>200008</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G12" s="5">
         <v>1</v>
@@ -7040,39 +7392,41 @@
         <v>80</v>
       </c>
       <c r="AL12" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="AM12" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="AM12" s="52"/>
+      <c r="AN12" s="52"/>
+      <c r="AO12" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="AN12" s="52"/>
-      <c r="AO12" s="5">
+      <c r="AP12" s="52"/>
+      <c r="AQ12" s="5">
         <v>2</v>
       </c>
-      <c r="AP12" s="55" t="s">
+      <c r="AR12" s="55" t="s">
         <v>79</v>
       </c>
-      <c r="AQ12">
+      <c r="AS12" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C12)</f>
-        <v>22</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>200009</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G13" s="5">
         <v>1</v>
@@ -7120,39 +7474,41 @@
         <v>81</v>
       </c>
       <c r="AL13" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="AM13" s="52" t="s">
+        <v>199</v>
+      </c>
+      <c r="AM13" s="52"/>
+      <c r="AN13" s="52"/>
+      <c r="AO13" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="AN13" s="52"/>
-      <c r="AO13" s="5">
+      <c r="AP13" s="52"/>
+      <c r="AQ13" s="5">
         <v>3</v>
       </c>
-      <c r="AP13" s="55" t="s">
+      <c r="AR13" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="AQ13">
+      <c r="AS13" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C13)</f>
-        <v>6</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>200010</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="s">
         <v>62</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G14" s="5">
         <v>1</v>
@@ -7198,33 +7554,35 @@
       <c r="AL14" s="52"/>
       <c r="AM14" s="52"/>
       <c r="AN14" s="52"/>
-      <c r="AO14" s="5">
+      <c r="AO14" s="52"/>
+      <c r="AP14" s="52"/>
+      <c r="AQ14" s="5">
         <v>3</v>
       </c>
-      <c r="AP14" s="55" t="s">
-        <v>162</v>
-      </c>
-      <c r="AQ14">
+      <c r="AR14" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="AS14" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C14)</f>
-        <v>4</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>200011</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G15" s="5">
         <v>1</v>
@@ -7269,40 +7627,42 @@
       <c r="AI15" s="44"/>
       <c r="AJ15" s="44"/>
       <c r="AK15" s="5" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AL15" s="52"/>
       <c r="AM15" s="52" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AN15" s="52"/>
-      <c r="AO15" s="5">
+      <c r="AO15" s="52"/>
+      <c r="AP15" s="52"/>
+      <c r="AQ15" s="5">
         <v>2</v>
       </c>
-      <c r="AP15" s="55" t="s">
-        <v>169</v>
-      </c>
-      <c r="AQ15">
+      <c r="AR15" s="55" t="s">
+        <v>168</v>
+      </c>
+      <c r="AS15" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C15)</f>
-        <v>9</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:46" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>200012</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="5" t="s">
         <v>57</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G16" s="5">
         <v>1</v>
@@ -7353,27 +7713,29 @@
       <c r="AI16" s="44"/>
       <c r="AJ16" s="44"/>
       <c r="AK16" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AL16" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM16" s="52" t="s">
-        <v>333</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="AM16" s="52"/>
       <c r="AN16" s="52"/>
-      <c r="AO16" s="5">
+      <c r="AO16" s="52" t="s">
+        <v>330</v>
+      </c>
+      <c r="AP16" s="52"/>
+      <c r="AQ16" s="5">
         <v>2</v>
       </c>
-      <c r="AP16" s="55" t="s">
+      <c r="AR16" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="AQ16">
+      <c r="AS16" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C16)</f>
-        <v>4</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>200013</v>
       </c>
@@ -7381,14 +7743,14 @@
         <v>39</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="5" t="s">
         <v>56</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G17" s="5">
         <v>1</v>
@@ -7435,42 +7797,44 @@
       <c r="AI17" s="44"/>
       <c r="AJ17" s="44"/>
       <c r="AK17" s="5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="AL17" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM17" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM17" s="52"/>
+      <c r="AN17" s="52"/>
+      <c r="AO17" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="AN17" s="52"/>
-      <c r="AO17" s="5">
+      <c r="AP17" s="52"/>
+      <c r="AQ17" s="5">
         <v>2</v>
       </c>
-      <c r="AP17" s="55" t="s">
+      <c r="AR17" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="AQ17">
+      <c r="AS17" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C17)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>200014</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G18" s="5">
         <v>1</v>
@@ -7518,39 +7882,41 @@
         <v>80</v>
       </c>
       <c r="AL18" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="AM18" s="52" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM18" s="52"/>
+      <c r="AN18" s="52"/>
+      <c r="AO18" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="AN18" s="52"/>
-      <c r="AO18" s="5">
+      <c r="AP18" s="52"/>
+      <c r="AQ18" s="5">
         <v>2</v>
       </c>
-      <c r="AP18" s="55" t="s">
-        <v>186</v>
-      </c>
-      <c r="AQ18">
+      <c r="AR18" s="55" t="s">
+        <v>185</v>
+      </c>
+      <c r="AS18" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C18)</f>
-        <v>20</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>200015</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G19" s="5">
         <v>1</v>
@@ -7597,42 +7963,44 @@
       <c r="AI19" s="44"/>
       <c r="AJ19" s="44"/>
       <c r="AK19" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AL19" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="AM19" s="52" t="s">
-        <v>189</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="AM19" s="52"/>
       <c r="AN19" s="52"/>
-      <c r="AO19" s="5">
+      <c r="AO19" s="52" t="s">
+        <v>188</v>
+      </c>
+      <c r="AP19" s="52"/>
+      <c r="AQ19" s="5">
         <v>2</v>
       </c>
-      <c r="AP19" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="AQ19">
+      <c r="AR19" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="AS19" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C19)</f>
-        <v>21</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>200016</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G20" s="5">
         <v>1</v>
@@ -7683,44 +8051,46 @@
       <c r="AI20" s="44"/>
       <c r="AJ20" s="44"/>
       <c r="AK20" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AL20" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM20" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM20" s="52"/>
+      <c r="AN20" s="52"/>
+      <c r="AO20" s="52" t="s">
         <v>68</v>
       </c>
-      <c r="AN20" s="52"/>
-      <c r="AO20" s="5">
+      <c r="AP20" s="52"/>
+      <c r="AQ20" s="5">
         <v>2</v>
       </c>
-      <c r="AP20" s="55" t="s">
-        <v>210</v>
-      </c>
-      <c r="AQ20">
+      <c r="AR20" s="55" t="s">
+        <v>209</v>
+      </c>
+      <c r="AS20" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C20)</f>
-        <v>6</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A21" s="27">
         <v>201002</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E21" s="47" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G21" s="47">
         <v>1</v>
@@ -7748,10 +8118,10 @@
         <v>1</v>
       </c>
       <c r="Z21" s="27" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AA21" s="27" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="AB21" s="61">
         <v>301001</v>
@@ -7767,40 +8137,42 @@
       <c r="AI21" s="45"/>
       <c r="AJ21" s="45"/>
       <c r="AK21" s="47" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="AL21" s="53"/>
       <c r="AM21" s="53"/>
       <c r="AN21" s="53"/>
-      <c r="AO21" s="47">
+      <c r="AO21" s="53"/>
+      <c r="AP21" s="53"/>
+      <c r="AQ21" s="47">
         <v>2</v>
       </c>
-      <c r="AP21" s="47" t="s">
-        <v>357</v>
-      </c>
-      <c r="AQ21">
+      <c r="AR21" s="47" t="s">
+        <v>354</v>
+      </c>
+      <c r="AS21" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C21)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>201003</v>
       </c>
       <c r="B22" s="14" t="s">
+        <v>348</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>354</v>
-      </c>
       <c r="D22" s="5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G22" s="5">
         <v>1</v>
@@ -7813,7 +8185,7 @@
         <v>103</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
@@ -7832,14 +8204,14 @@
         <v>1</v>
       </c>
       <c r="Z22" s="8" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AA22" s="8"/>
       <c r="AB22" s="60">
         <v>301001</v>
       </c>
       <c r="AC22" s="49" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AD22" s="5"/>
       <c r="AE22" s="44"/>
@@ -7849,38 +8221,40 @@
       <c r="AI22" s="44"/>
       <c r="AJ22" s="44"/>
       <c r="AK22" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AL22" s="52"/>
       <c r="AM22" s="52"/>
       <c r="AN22" s="52"/>
-      <c r="AO22" s="5">
+      <c r="AO22" s="52"/>
+      <c r="AP22" s="52"/>
+      <c r="AQ22" s="5">
         <v>2</v>
       </c>
-      <c r="AP22" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="AQ22">
+      <c r="AR22" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="AS22" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C22)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>201004</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G23" s="5">
         <v>1</v>
@@ -7919,38 +8293,40 @@
       <c r="AI23" s="44"/>
       <c r="AJ23" s="44"/>
       <c r="AK23" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AL23" s="52"/>
       <c r="AM23" s="52"/>
       <c r="AN23" s="52"/>
-      <c r="AO23" s="5">
+      <c r="AO23" s="52"/>
+      <c r="AP23" s="52"/>
+      <c r="AQ23" s="5">
         <v>2</v>
       </c>
-      <c r="AP23" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="AQ23">
+      <c r="AR23" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="AS23" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C23)</f>
-        <v>5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>201005</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D24" s="5"/>
       <c r="E24" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G24" s="5">
         <v>1</v>
@@ -7980,7 +8356,7 @@
         <v>1</v>
       </c>
       <c r="Z24" s="8" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AA24" s="8"/>
       <c r="AB24" s="5"/>
@@ -7993,38 +8369,40 @@
       <c r="AI24" s="44"/>
       <c r="AJ24" s="44"/>
       <c r="AK24" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AL24" s="52"/>
       <c r="AM24" s="52"/>
       <c r="AN24" s="52"/>
-      <c r="AO24" s="5">
+      <c r="AO24" s="52"/>
+      <c r="AP24" s="52"/>
+      <c r="AQ24" s="5">
         <v>4</v>
       </c>
-      <c r="AP24" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="AQ24">
+      <c r="AR24" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="AS24" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C24)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>201006</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G25" s="5">
         <v>1</v>
@@ -8038,7 +8416,7 @@
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -8067,42 +8445,44 @@
       <c r="AI25" s="44"/>
       <c r="AJ25" s="44"/>
       <c r="AK25" s="5" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="AL25" s="52" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AM25" s="52"/>
       <c r="AN25" s="52"/>
-      <c r="AO25" s="5">
+      <c r="AO25" s="52"/>
+      <c r="AP25" s="52"/>
+      <c r="AQ25" s="5">
         <v>2</v>
       </c>
-      <c r="AP25" s="55" t="s">
+      <c r="AR25" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="AQ25">
+      <c r="AS25" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C25)</f>
-        <v>7</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>201007</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G26" s="5">
         <v>1</v>
@@ -8112,7 +8492,7 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
@@ -8132,10 +8512,10 @@
         <v>1</v>
       </c>
       <c r="Z26" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="AA26" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="AB26" s="5"/>
       <c r="AC26" s="5"/>
@@ -8147,35 +8527,37 @@
       <c r="AI26" s="44"/>
       <c r="AJ26" s="44"/>
       <c r="AK26" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AL26" s="52"/>
       <c r="AM26" s="52"/>
       <c r="AN26" s="52"/>
-      <c r="AO26" s="5">
+      <c r="AO26" s="52"/>
+      <c r="AP26" s="52"/>
+      <c r="AQ26" s="5">
         <v>1</v>
       </c>
-      <c r="AP26" s="55" t="s">
-        <v>362</v>
-      </c>
-      <c r="AQ26">
+      <c r="AR26" s="55" t="s">
+        <v>359</v>
+      </c>
+      <c r="AS26" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C26)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>201008</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F27" s="8"/>
       <c r="G27" s="5">
@@ -8190,7 +8572,7 @@
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
@@ -8221,39 +8603,41 @@
       <c r="AI27" s="44"/>
       <c r="AJ27" s="44"/>
       <c r="AK27" s="5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="AL27" s="52" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AM27" s="52"/>
       <c r="AN27" s="52"/>
-      <c r="AO27" s="5">
+      <c r="AO27" s="52"/>
+      <c r="AP27" s="52"/>
+      <c r="AQ27" s="5">
         <v>3</v>
       </c>
-      <c r="AP27" s="55" t="s">
+      <c r="AR27" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="AQ27">
+      <c r="AS27" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C27)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>201009</v>
       </c>
       <c r="B28" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>552</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>555</v>
-      </c>
       <c r="D28" s="5" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F28" s="8"/>
       <c r="G28" s="5">
@@ -8268,7 +8652,7 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
@@ -8301,25 +8685,27 @@
       <c r="AI28" s="44"/>
       <c r="AJ28" s="44"/>
       <c r="AK28" s="5" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AL28" s="52" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AM28" s="52"/>
       <c r="AN28" s="52"/>
-      <c r="AO28" s="5">
+      <c r="AO28" s="52"/>
+      <c r="AP28" s="52"/>
+      <c r="AQ28" s="5">
         <v>4</v>
       </c>
-      <c r="AP28" s="55" t="s">
-        <v>553</v>
-      </c>
-      <c r="AQ28">
+      <c r="AR28" s="55" t="s">
+        <v>550</v>
+      </c>
+      <c r="AS28" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C28)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>201010</v>
       </c>
@@ -8327,14 +8713,14 @@
         <v>54</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5" t="s">
         <v>82</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G29" s="5">
         <v>1</v>
@@ -8381,42 +8767,44 @@
       <c r="AI29" s="44"/>
       <c r="AJ29" s="44"/>
       <c r="AK29" s="5" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="AL29" s="52" t="s">
+        <v>172</v>
+      </c>
+      <c r="AM29" s="52" t="s">
         <v>173</v>
       </c>
-      <c r="AM29" s="52" t="s">
-        <v>174</v>
-      </c>
       <c r="AN29" s="52"/>
-      <c r="AO29" s="5">
+      <c r="AO29" s="52"/>
+      <c r="AP29" s="52"/>
+      <c r="AQ29" s="5">
         <v>3</v>
       </c>
-      <c r="AP29" s="55" t="s">
+      <c r="AR29" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="AQ29">
+      <c r="AS29" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C29)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>201011</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
         <v>87</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G30" s="5">
         <v>1</v>
@@ -8455,7 +8843,7 @@
       <c r="AC30" s="5"/>
       <c r="AD30" s="5"/>
       <c r="AE30" s="44" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="AF30" s="44"/>
       <c r="AG30" s="44">
@@ -8469,44 +8857,46 @@
       </c>
       <c r="AJ30" s="44"/>
       <c r="AK30" s="5" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="AL30" s="52" t="s">
-        <v>199</v>
-      </c>
-      <c r="AM30" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="AM30" s="52"/>
+      <c r="AN30" s="52" t="s">
         <v>83</v>
       </c>
-      <c r="AN30" s="52">
+      <c r="AO30" s="52"/>
+      <c r="AP30" s="52">
         <v>5</v>
       </c>
-      <c r="AO30" s="5">
+      <c r="AQ30" s="5">
         <v>4</v>
       </c>
-      <c r="AP30" s="55" t="s">
+      <c r="AR30" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="AQ30">
+      <c r="AS30" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C30)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>201012</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G31" s="5">
         <v>1</v>
@@ -8545,7 +8935,7 @@
       <c r="AC31" s="5"/>
       <c r="AD31" s="5"/>
       <c r="AE31" s="44" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AF31" s="44">
         <v>1</v>
@@ -8564,26 +8954,28 @@
         <v>90</v>
       </c>
       <c r="AL31" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM31" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="AM31" s="52"/>
+      <c r="AN31" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="AN31" s="52">
+      <c r="AO31" s="52"/>
+      <c r="AP31" s="52">
         <v>1.6</v>
       </c>
-      <c r="AO31" s="5">
+      <c r="AQ31" s="5">
         <v>2</v>
       </c>
-      <c r="AP31" s="55" t="s">
-        <v>519</v>
-      </c>
-      <c r="AQ31">
+      <c r="AR31" s="55" t="s">
+        <v>516</v>
+      </c>
+      <c r="AS31" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C31)</f>
-        <v>5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>201013</v>
       </c>
@@ -8591,14 +8983,14 @@
         <v>89</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5" t="s">
         <v>92</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G32" s="5">
         <v>1</v>
@@ -8637,7 +9029,7 @@
       <c r="AC32" s="5"/>
       <c r="AD32" s="5"/>
       <c r="AE32" s="44" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AF32" s="44">
         <v>5</v>
@@ -8656,41 +9048,43 @@
         <v>90</v>
       </c>
       <c r="AL32" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM32" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="AM32" s="52"/>
+      <c r="AN32" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="AN32" s="52">
+      <c r="AO32" s="52"/>
+      <c r="AP32" s="52">
         <v>1.6</v>
       </c>
-      <c r="AO32" s="5">
+      <c r="AQ32" s="5">
         <v>4</v>
       </c>
-      <c r="AP32" s="55" t="s">
+      <c r="AR32" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="AQ32">
+      <c r="AS32" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C32)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>201014</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="5" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G33" s="5">
         <v>1</v>
@@ -8706,7 +9100,7 @@
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
@@ -8733,7 +9127,7 @@
       <c r="AC33" s="5"/>
       <c r="AD33" s="5"/>
       <c r="AE33" s="44" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="AF33" s="44"/>
       <c r="AG33" s="44">
@@ -8747,46 +9141,48 @@
         <v>40</v>
       </c>
       <c r="AK33" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AL33" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM33" s="52" t="s">
-        <v>558</v>
-      </c>
-      <c r="AN33" s="52">
+        <v>200</v>
+      </c>
+      <c r="AM33" s="52"/>
+      <c r="AN33" s="52"/>
+      <c r="AO33" s="52" t="s">
+        <v>555</v>
+      </c>
+      <c r="AP33" s="52">
         <v>3</v>
       </c>
-      <c r="AO33" s="5">
+      <c r="AQ33" s="5">
         <v>2</v>
       </c>
-      <c r="AP33" s="55" t="s">
-        <v>559</v>
-      </c>
-      <c r="AQ33">
+      <c r="AR33" s="55" t="s">
+        <v>556</v>
+      </c>
+      <c r="AS33" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C33)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>201015</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G34" s="5">
         <v>1</v>
@@ -8833,44 +9229,46 @@
       <c r="AI34" s="44"/>
       <c r="AJ34" s="44"/>
       <c r="AK34" s="5" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="AL34" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM34" s="52" t="s">
-        <v>594</v>
-      </c>
-      <c r="AN34" s="52">
+        <v>207</v>
+      </c>
+      <c r="AM34" s="52"/>
+      <c r="AN34" s="52"/>
+      <c r="AO34" s="52" t="s">
+        <v>591</v>
+      </c>
+      <c r="AP34" s="52">
         <v>3</v>
       </c>
-      <c r="AO34" s="5">
+      <c r="AQ34" s="5">
         <v>2</v>
       </c>
-      <c r="AP34" s="55" t="s">
-        <v>598</v>
-      </c>
-      <c r="AQ34">
+      <c r="AR34" s="55" t="s">
+        <v>595</v>
+      </c>
+      <c r="AS34" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C34)</f>
-        <v>5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>201016</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G35" s="5">
         <v>1</v>
@@ -8913,7 +9311,7 @@
       <c r="AC35" s="5"/>
       <c r="AD35" s="5"/>
       <c r="AE35" s="44" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="AF35" s="44"/>
       <c r="AG35" s="44">
@@ -8927,29 +9325,31 @@
         <v>40</v>
       </c>
       <c r="AK35" s="5" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="AL35" s="52" t="s">
-        <v>173</v>
-      </c>
-      <c r="AM35" s="52" t="s">
-        <v>220</v>
-      </c>
-      <c r="AN35" s="52">
+        <v>172</v>
+      </c>
+      <c r="AM35" s="52"/>
+      <c r="AN35" s="52"/>
+      <c r="AO35" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="AP35" s="52">
         <v>4</v>
       </c>
-      <c r="AO35" s="5">
+      <c r="AQ35" s="5">
         <v>3</v>
       </c>
-      <c r="AP35" s="55" t="s">
-        <v>566</v>
-      </c>
-      <c r="AQ35">
+      <c r="AR35" s="55" t="s">
+        <v>563</v>
+      </c>
+      <c r="AS35" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C35)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>201017</v>
       </c>
@@ -8957,11 +9357,11 @@
         <v>105</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="5">
@@ -9007,37 +9407,39 @@
       <c r="AI36" s="44"/>
       <c r="AJ36" s="44"/>
       <c r="AK36" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AL36" s="52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM36" s="52"/>
       <c r="AN36" s="52"/>
-      <c r="AO36" s="5">
+      <c r="AO36" s="52"/>
+      <c r="AP36" s="52"/>
+      <c r="AQ36" s="5">
         <v>3</v>
       </c>
-      <c r="AP36" s="55" t="s">
+      <c r="AR36" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="AQ36">
+      <c r="AS36" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C36)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>201018</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F37" s="8"/>
       <c r="G37" s="5">
@@ -9052,7 +9454,7 @@
         <v>0.3</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
@@ -9081,35 +9483,37 @@
       <c r="AI37" s="44"/>
       <c r="AJ37" s="44"/>
       <c r="AK37" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AL37" s="52" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM37" s="52" t="s">
+        <v>200</v>
+      </c>
+      <c r="AM37" s="52"/>
+      <c r="AN37" s="52"/>
+      <c r="AO37" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="AP37" s="52"/>
+      <c r="AQ37" s="5">
+        <v>3</v>
+      </c>
+      <c r="AR37" s="55" t="s">
         <v>242</v>
       </c>
-      <c r="AN37" s="52"/>
-      <c r="AO37" s="5">
-        <v>3</v>
-      </c>
-      <c r="AP37" s="55" t="s">
-        <v>244</v>
-      </c>
-      <c r="AQ37">
+      <c r="AS37" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C37)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>201019</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5" t="s">
@@ -9128,7 +9532,7 @@
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
@@ -9164,22 +9568,24 @@
         <v>111</v>
       </c>
       <c r="AL38" s="52"/>
-      <c r="AM38" s="52" t="s">
+      <c r="AM38" s="52"/>
+      <c r="AN38" s="52"/>
+      <c r="AO38" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="AN38" s="52"/>
-      <c r="AO38" s="5">
+      <c r="AP38" s="52"/>
+      <c r="AQ38" s="5">
         <v>2</v>
       </c>
-      <c r="AP38" s="55" t="s">
-        <v>445</v>
-      </c>
-      <c r="AQ38">
+      <c r="AR38" s="55" t="s">
+        <v>442</v>
+      </c>
+      <c r="AS38" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C38)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>201020</v>
       </c>
@@ -9187,11 +9593,11 @@
         <v>116</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="5">
@@ -9206,7 +9612,7 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
@@ -9242,24 +9648,26 @@
         <v>115</v>
       </c>
       <c r="AL39" s="52" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AM39" s="52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AN39" s="52"/>
-      <c r="AO39" s="5">
+      <c r="AO39" s="52"/>
+      <c r="AP39" s="52"/>
+      <c r="AQ39" s="5">
         <v>1</v>
       </c>
-      <c r="AP39" s="55" t="s">
+      <c r="AR39" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="AQ39">
+      <c r="AS39" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C39)</f>
-        <v>4</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>201021</v>
       </c>
@@ -9267,14 +9675,14 @@
         <v>128</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5" t="s">
         <v>135</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G40" s="5">
         <v>1</v>
@@ -9313,7 +9721,7 @@
       <c r="AC40" s="5"/>
       <c r="AD40" s="5"/>
       <c r="AE40" s="44" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AF40" s="44">
         <v>1</v>
@@ -9332,26 +9740,28 @@
         <v>90</v>
       </c>
       <c r="AL40" s="52" t="s">
-        <v>200</v>
-      </c>
-      <c r="AM40" s="52" t="s">
-        <v>219</v>
-      </c>
-      <c r="AN40" s="52">
+        <v>199</v>
+      </c>
+      <c r="AM40" s="52"/>
+      <c r="AN40" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO40" s="52"/>
+      <c r="AP40" s="52">
         <v>1.6</v>
       </c>
-      <c r="AO40" s="5">
+      <c r="AQ40" s="5">
         <v>2</v>
       </c>
-      <c r="AP40" s="55" t="s">
+      <c r="AR40" s="55" t="s">
         <v>136</v>
       </c>
-      <c r="AQ40">
+      <c r="AS40" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C40)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>201022</v>
       </c>
@@ -9359,14 +9769,14 @@
         <v>148</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5" t="s">
         <v>149</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G41" s="5">
         <v>1</v>
@@ -9380,7 +9790,7 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
@@ -9416,24 +9826,26 @@
         <v>139</v>
       </c>
       <c r="AL41" s="52" t="s">
-        <v>246</v>
-      </c>
-      <c r="AM41" s="52" t="s">
+        <v>243</v>
+      </c>
+      <c r="AM41" s="52"/>
+      <c r="AN41" s="52"/>
+      <c r="AO41" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="AN41" s="52"/>
-      <c r="AO41" s="5">
+      <c r="AP41" s="52"/>
+      <c r="AQ41" s="5">
         <v>4</v>
       </c>
-      <c r="AP41" s="55" t="s">
+      <c r="AR41" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="AQ41">
+      <c r="AS41" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C41)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>201023</v>
       </c>
@@ -9441,14 +9853,14 @@
         <v>151</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="5" t="s">
         <v>152</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G42" s="5">
         <v>1</v>
@@ -9498,38 +9910,40 @@
         <v>139</v>
       </c>
       <c r="AL42" s="52" t="s">
-        <v>246</v>
-      </c>
-      <c r="AM42" s="52" t="s">
+        <v>243</v>
+      </c>
+      <c r="AM42" s="52"/>
+      <c r="AN42" s="52"/>
+      <c r="AO42" s="52" t="s">
         <v>153</v>
       </c>
-      <c r="AN42" s="52"/>
-      <c r="AO42" s="5">
+      <c r="AP42" s="52"/>
+      <c r="AQ42" s="5">
         <v>3</v>
       </c>
-      <c r="AP42" s="55" t="s">
+      <c r="AR42" s="55" t="s">
         <v>154</v>
       </c>
-      <c r="AQ42">
+      <c r="AS42" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C42)</f>
-        <v>4</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>201024</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5">
@@ -9573,42 +9987,44 @@
       <c r="AI43" s="44"/>
       <c r="AJ43" s="44"/>
       <c r="AK43" s="5" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="AL43" s="52" t="s">
-        <v>307</v>
-      </c>
-      <c r="AM43" s="52" t="s">
+        <v>304</v>
+      </c>
+      <c r="AM43" s="52"/>
+      <c r="AN43" s="52"/>
+      <c r="AO43" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="AN43" s="52"/>
-      <c r="AO43" s="5">
+      <c r="AP43" s="52"/>
+      <c r="AQ43" s="5">
         <v>1</v>
       </c>
-      <c r="AP43" t="s">
-        <v>607</v>
-      </c>
-      <c r="AQ43">
+      <c r="AR43" t="s">
+        <v>604</v>
+      </c>
+      <c r="AS43" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C43)</f>
-        <v>6</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>201025</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="5" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="G44" s="5">
         <v>1</v>
@@ -9649,40 +10065,42 @@
       <c r="AI44" s="44"/>
       <c r="AJ44" s="44"/>
       <c r="AK44" s="59" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="AL44" s="52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM44" s="52"/>
       <c r="AN44" s="52"/>
-      <c r="AO44" s="5">
+      <c r="AO44" s="52"/>
+      <c r="AP44" s="52"/>
+      <c r="AQ44" s="5">
         <v>1</v>
       </c>
-      <c r="AP44" t="s">
-        <v>585</v>
-      </c>
-      <c r="AQ44">
+      <c r="AR44" t="s">
+        <v>582</v>
+      </c>
+      <c r="AS44" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C44)</f>
-        <v>7</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A45" s="29">
         <v>202001</v>
       </c>
       <c r="B45" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C45" s="29" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D45" s="47"/>
       <c r="E45" s="47" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F45" s="30" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G45" s="47">
         <v>1</v>
@@ -9694,10 +10112,10 @@
       <c r="J45" s="47"/>
       <c r="K45" s="47"/>
       <c r="L45" s="47" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="M45" s="47" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="N45" s="47">
         <v>20</v>
@@ -9727,25 +10145,27 @@
       <c r="AI45" s="45"/>
       <c r="AJ45" s="45"/>
       <c r="AK45" s="47" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AL45" s="53"/>
-      <c r="AM45" s="53" t="s">
+      <c r="AM45" s="53"/>
+      <c r="AN45" s="53"/>
+      <c r="AO45" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="AN45" s="53"/>
-      <c r="AO45" s="47">
+      <c r="AP45" s="53"/>
+      <c r="AQ45" s="47">
         <v>2</v>
       </c>
-      <c r="AP45" s="56" t="s">
+      <c r="AR45" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="AQ45">
+      <c r="AS45" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C45)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>202002</v>
       </c>
@@ -9753,7 +10173,7 @@
         <v>66</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="5" t="s">
@@ -9775,7 +10195,7 @@
         <v>130</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
@@ -9803,23 +10223,25 @@
       <c r="AI46" s="44"/>
       <c r="AJ46" s="44"/>
       <c r="AK46" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="AL46" s="52"/>
       <c r="AM46" s="52"/>
       <c r="AN46" s="52"/>
-      <c r="AO46" s="5">
+      <c r="AO46" s="52"/>
+      <c r="AP46" s="52"/>
+      <c r="AQ46" s="5">
         <v>3</v>
       </c>
-      <c r="AP46" s="57" t="s">
+      <c r="AR46" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="AQ46">
+      <c r="AS46" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C46)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>202003</v>
       </c>
@@ -9827,16 +10249,16 @@
         <v>119</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G47" s="5">
         <v>1</v>
@@ -9848,10 +10270,10 @@
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
       <c r="L47" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="49"/>
@@ -9870,7 +10292,7 @@
         <v>1</v>
       </c>
       <c r="Z47" s="8" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AA47" s="8"/>
       <c r="AB47" s="5"/>
@@ -9883,40 +10305,42 @@
       <c r="AI47" s="44"/>
       <c r="AJ47" s="44"/>
       <c r="AK47" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AL47" s="52"/>
-      <c r="AM47" s="52" t="s">
+      <c r="AM47" s="52"/>
+      <c r="AN47" s="52"/>
+      <c r="AO47" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="AN47" s="52"/>
-      <c r="AO47" s="5">
+      <c r="AP47" s="52"/>
+      <c r="AQ47" s="5">
         <v>3</v>
       </c>
-      <c r="AP47" s="57" t="s">
+      <c r="AR47" s="57" t="s">
         <v>120</v>
       </c>
-      <c r="AQ47">
+      <c r="AS47" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C47)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>202004</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G48" s="5">
         <v>1</v>
@@ -9928,10 +10352,10 @@
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="49"/>
@@ -9959,37 +10383,39 @@
       <c r="AI48" s="44"/>
       <c r="AJ48" s="44"/>
       <c r="AK48" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="AL48" s="52"/>
-      <c r="AM48" s="52" t="s">
+      <c r="AM48" s="52"/>
+      <c r="AN48" s="52"/>
+      <c r="AO48" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="AN48" s="52"/>
-      <c r="AO48" s="5">
+      <c r="AP48" s="52"/>
+      <c r="AQ48" s="5">
         <v>1</v>
       </c>
-      <c r="AP48" s="57" t="s">
-        <v>370</v>
-      </c>
-      <c r="AQ48">
+      <c r="AR48" s="57" t="s">
+        <v>367</v>
+      </c>
+      <c r="AS48" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C48)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>202005</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="5">
@@ -10041,42 +10467,44 @@
       <c r="AI49" s="44"/>
       <c r="AJ49" s="44"/>
       <c r="AK49" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AL49" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM49" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM49" s="52"/>
+      <c r="AN49" s="52"/>
+      <c r="AO49" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="AN49" s="52"/>
-      <c r="AO49" s="5">
+      <c r="AP49" s="52"/>
+      <c r="AQ49" s="5">
         <v>1</v>
       </c>
-      <c r="AP49" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="AQ49">
+      <c r="AR49" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="AS49" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C49)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>202006</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G50" s="5">
         <v>1</v>
@@ -10121,40 +10549,42 @@
       <c r="AI50" s="44"/>
       <c r="AJ50" s="44"/>
       <c r="AK50" s="5" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AL50" s="52"/>
       <c r="AM50" s="52"/>
       <c r="AN50" s="52"/>
-      <c r="AO50" s="5">
+      <c r="AO50" s="52"/>
+      <c r="AP50" s="52"/>
+      <c r="AQ50" s="5">
         <v>3</v>
       </c>
-      <c r="AP50" s="57" t="s">
-        <v>310</v>
-      </c>
-      <c r="AQ50">
+      <c r="AR50" s="57" t="s">
+        <v>307</v>
+      </c>
+      <c r="AS50" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C50)</f>
-        <v>5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>202007</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G51" s="5">
         <v>1</v>
@@ -10171,7 +10601,7 @@
         <v>103</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="N51" s="5"/>
       <c r="O51" s="5"/>
@@ -10190,7 +10620,7 @@
         <v>1</v>
       </c>
       <c r="Z51" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AA51" s="8"/>
       <c r="AB51" s="5"/>
@@ -10203,38 +10633,40 @@
       <c r="AI51" s="44"/>
       <c r="AJ51" s="44"/>
       <c r="AK51" s="5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AL51" s="52"/>
       <c r="AM51" s="52"/>
       <c r="AN51" s="52"/>
-      <c r="AO51" s="5">
+      <c r="AO51" s="52"/>
+      <c r="AP51" s="52"/>
+      <c r="AQ51" s="5">
         <v>3</v>
       </c>
-      <c r="AP51" s="57" t="s">
-        <v>408</v>
-      </c>
-      <c r="AQ51">
+      <c r="AR51" s="57" t="s">
+        <v>405</v>
+      </c>
+      <c r="AS51" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C51)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>202008</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G52" s="5">
         <v>1</v>
@@ -10251,7 +10683,7 @@
         <v>103</v>
       </c>
       <c r="M52" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
@@ -10279,40 +10711,42 @@
       <c r="AI52" s="44"/>
       <c r="AJ52" s="44"/>
       <c r="AK52" s="5" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="AL52" s="52"/>
       <c r="AM52" s="52"/>
       <c r="AN52" s="52"/>
-      <c r="AO52" s="5">
+      <c r="AO52" s="52"/>
+      <c r="AP52" s="52"/>
+      <c r="AQ52" s="5">
         <v>1</v>
       </c>
-      <c r="AP52" s="57" t="s">
-        <v>407</v>
-      </c>
-      <c r="AQ52">
+      <c r="AR52" s="57" t="s">
+        <v>404</v>
+      </c>
+      <c r="AS52" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C52)</f>
-        <v>3</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>202009</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G53" s="5">
         <v>1</v>
@@ -10325,7 +10759,7 @@
         <v>103</v>
       </c>
       <c r="M53" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="N53" s="5"/>
       <c r="O53" s="5"/>
@@ -10344,12 +10778,12 @@
         <v>1</v>
       </c>
       <c r="Z53" s="8" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AA53" s="8"/>
       <c r="AB53" s="5"/>
       <c r="AC53" s="49" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AD53" s="5"/>
       <c r="AE53" s="44"/>
@@ -10359,38 +10793,40 @@
       <c r="AI53" s="44"/>
       <c r="AJ53" s="44"/>
       <c r="AK53" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AL53" s="52"/>
       <c r="AM53" s="52"/>
       <c r="AN53" s="52"/>
-      <c r="AO53" s="5">
+      <c r="AO53" s="52"/>
+      <c r="AP53" s="52"/>
+      <c r="AQ53" s="5">
         <v>3</v>
       </c>
-      <c r="AP53" s="5" t="s">
-        <v>422</v>
-      </c>
-      <c r="AQ53">
+      <c r="AR53" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="AS53" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C53)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A54" s="10">
         <v>202010</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="D54" s="5"/>
       <c r="E54" s="5" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G54" s="5">
         <v>1</v>
@@ -10403,7 +10839,7 @@
         <v>103</v>
       </c>
       <c r="M54" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="N54" s="5"/>
       <c r="O54" s="5"/>
@@ -10423,7 +10859,7 @@
       <c r="AA54" s="8"/>
       <c r="AB54" s="5"/>
       <c r="AC54" s="49" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AD54" s="5"/>
       <c r="AE54" s="44"/>
@@ -10433,38 +10869,40 @@
       <c r="AI54" s="44"/>
       <c r="AJ54" s="44"/>
       <c r="AK54" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AL54" s="52"/>
       <c r="AM54" s="52"/>
       <c r="AN54" s="52"/>
-      <c r="AO54" s="5">
+      <c r="AO54" s="52"/>
+      <c r="AP54" s="52"/>
+      <c r="AQ54" s="5">
         <v>1</v>
       </c>
-      <c r="AP54" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="AQ54">
+      <c r="AR54" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="AS54" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C54)</f>
-        <v>3</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A55" s="10">
         <v>202011</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G55" s="5">
         <v>1</v>
@@ -10503,40 +10941,42 @@
       <c r="AI55" s="44"/>
       <c r="AJ55" s="44"/>
       <c r="AK55" s="5" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AL55" s="52"/>
       <c r="AM55" s="52"/>
       <c r="AN55" s="52"/>
-      <c r="AO55" s="5">
+      <c r="AO55" s="52"/>
+      <c r="AP55" s="52"/>
+      <c r="AQ55" s="5">
         <v>1</v>
       </c>
-      <c r="AP55" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="AQ55">
+      <c r="AR55" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="AS55" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C55)</f>
-        <v>6</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A56" s="10">
         <v>202012</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G56" s="5">
         <v>1</v>
@@ -10566,7 +11006,7 @@
         <v>2</v>
       </c>
       <c r="Z56" s="8" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AA56" s="8"/>
       <c r="AB56" s="5"/>
@@ -10579,38 +11019,40 @@
       <c r="AI56" s="44"/>
       <c r="AJ56" s="44"/>
       <c r="AK56" s="5" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AL56" s="52"/>
       <c r="AM56" s="52"/>
       <c r="AN56" s="52"/>
-      <c r="AO56" s="5">
+      <c r="AO56" s="52"/>
+      <c r="AP56" s="52"/>
+      <c r="AQ56" s="5">
         <v>2</v>
       </c>
-      <c r="AP56" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="AQ56">
+      <c r="AR56" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="AS56" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C56)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A57" s="10">
         <v>202013</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D57" s="5"/>
       <c r="E57" s="5" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G57" s="5">
         <v>1</v>
@@ -10649,40 +11091,42 @@
       <c r="AI57" s="44"/>
       <c r="AJ57" s="44"/>
       <c r="AK57" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AL57" s="52"/>
       <c r="AM57" s="52"/>
       <c r="AN57" s="52"/>
-      <c r="AO57" s="5">
+      <c r="AO57" s="52"/>
+      <c r="AP57" s="52"/>
+      <c r="AQ57" s="5">
         <v>1</v>
       </c>
-      <c r="AP57" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="AQ57">
+      <c r="AR57" s="5" t="s">
+        <v>492</v>
+      </c>
+      <c r="AS57" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C57)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A58" s="31">
         <v>202014</v>
       </c>
       <c r="B58" s="32" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C58" s="31" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D58" s="48" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E58" s="48" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="G58" s="48">
         <v>1</v>
@@ -10712,7 +11156,7 @@
         <v>3</v>
       </c>
       <c r="Z58" s="43" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AA58" s="43"/>
       <c r="AB58" s="48"/>
@@ -10725,23 +11169,25 @@
       <c r="AI58" s="46"/>
       <c r="AJ58" s="46"/>
       <c r="AK58" s="48" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AL58" s="54"/>
       <c r="AM58" s="54"/>
       <c r="AN58" s="54"/>
-      <c r="AO58" s="48">
+      <c r="AO58" s="54"/>
+      <c r="AP58" s="54"/>
+      <c r="AQ58" s="48">
         <v>2</v>
       </c>
-      <c r="AP58" s="48" t="s">
-        <v>491</v>
-      </c>
-      <c r="AQ58">
+      <c r="AR58" s="48" t="s">
+        <v>488</v>
+      </c>
+      <c r="AS58" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C58)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="59" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A59" s="25">
         <v>203002</v>
       </c>
@@ -10749,16 +11195,16 @@
         <v>95</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D59" s="47" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E59" s="47" t="s">
         <v>100</v>
       </c>
       <c r="F59" s="27" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G59" s="47">
         <v>1</v>
@@ -10780,7 +11226,7 @@
       </c>
       <c r="O59" s="47"/>
       <c r="P59" s="47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q59" s="47">
         <v>1</v>
@@ -10814,36 +11260,38 @@
         <v>96</v>
       </c>
       <c r="AL59" s="53" t="s">
-        <v>175</v>
-      </c>
-      <c r="AM59" s="53" t="s">
-        <v>198</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="AM59" s="53"/>
       <c r="AN59" s="53"/>
-      <c r="AO59" s="47">
+      <c r="AO59" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="AP59" s="53"/>
+      <c r="AQ59" s="47">
         <v>4</v>
       </c>
-      <c r="AP59" s="56" t="s">
+      <c r="AR59" s="56" t="s">
         <v>101</v>
       </c>
-      <c r="AQ59">
+      <c r="AS59" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C59)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A60" s="9">
         <v>203003</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D60" s="5"/>
       <c r="E60" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F60" s="9"/>
       <c r="G60" s="5">
@@ -10887,25 +11335,27 @@
       <c r="AI60" s="44"/>
       <c r="AJ60" s="44"/>
       <c r="AK60" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AL60" s="52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM60" s="52"/>
       <c r="AN60" s="52"/>
-      <c r="AO60" s="5">
+      <c r="AO60" s="52"/>
+      <c r="AP60" s="52"/>
+      <c r="AQ60" s="5">
         <v>2</v>
       </c>
-      <c r="AP60" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="AQ60">
+      <c r="AR60" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="AS60" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C60)</f>
-        <v>7</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A61" s="9">
         <v>203004</v>
       </c>
@@ -10913,11 +11363,11 @@
         <v>126</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F61" s="9"/>
       <c r="G61" s="5">
@@ -10940,7 +11390,7 @@
       </c>
       <c r="O61" s="5"/>
       <c r="P61" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q61" s="5">
         <v>3</v>
@@ -10972,36 +11422,38 @@
         <v>96</v>
       </c>
       <c r="AL61" s="52" t="s">
-        <v>199</v>
-      </c>
-      <c r="AM61" s="52" t="s">
-        <v>197</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="AM61" s="52"/>
       <c r="AN61" s="52"/>
-      <c r="AO61" s="5">
+      <c r="AO61" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="AP61" s="52"/>
+      <c r="AQ61" s="5">
         <v>4</v>
       </c>
-      <c r="AP61" s="57" t="s">
+      <c r="AR61" s="57" t="s">
         <v>127</v>
       </c>
-      <c r="AQ61">
+      <c r="AS61" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C61)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A62" s="9">
         <v>203005</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D62" s="5"/>
       <c r="E62" s="5" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="F62" s="9"/>
       <c r="G62" s="5">
@@ -11052,36 +11504,38 @@
         <v>80</v>
       </c>
       <c r="AL62" s="52" t="s">
-        <v>203</v>
-      </c>
-      <c r="AM62" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="AM62" s="52"/>
+      <c r="AN62" s="52"/>
+      <c r="AO62" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="AN62" s="52"/>
-      <c r="AO62" s="5">
+      <c r="AP62" s="52"/>
+      <c r="AQ62" s="5">
         <v>2</v>
       </c>
-      <c r="AP62" s="57" t="s">
-        <v>160</v>
-      </c>
-      <c r="AQ62">
+      <c r="AR62" s="57" t="s">
+        <v>159</v>
+      </c>
+      <c r="AS62" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C62)</f>
-        <v>5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A63" s="9">
         <v>203006</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="F63" s="9"/>
       <c r="G63" s="5">
@@ -11096,7 +11550,7 @@
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
@@ -11132,36 +11586,38 @@
         <v>80</v>
       </c>
       <c r="AL63" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM63" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM63" s="52"/>
+      <c r="AN63" s="52"/>
+      <c r="AO63" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="AN63" s="52"/>
-      <c r="AO63" s="5">
+      <c r="AP63" s="52"/>
+      <c r="AQ63" s="5">
         <v>2</v>
       </c>
-      <c r="AP63" s="57" t="s">
-        <v>592</v>
-      </c>
-      <c r="AQ63">
+      <c r="AR63" s="57" t="s">
+        <v>589</v>
+      </c>
+      <c r="AS63" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C63)</f>
-        <v>5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A64" s="9">
         <v>203007</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="D64" s="5"/>
       <c r="E64" s="5" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="F64" s="9"/>
       <c r="G64" s="5">
@@ -11210,36 +11666,38 @@
         <v>80</v>
       </c>
       <c r="AL64" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM64" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM64" s="52"/>
+      <c r="AN64" s="52"/>
+      <c r="AO64" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="AN64" s="52"/>
-      <c r="AO64" s="5">
+      <c r="AP64" s="52"/>
+      <c r="AQ64" s="5">
         <v>2</v>
       </c>
-      <c r="AP64" s="57" t="s">
-        <v>633</v>
-      </c>
-      <c r="AQ64">
+      <c r="AR64" s="57" t="s">
+        <v>630</v>
+      </c>
+      <c r="AS64" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C64)</f>
-        <v>5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A65" s="9">
         <v>203008</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="5">
@@ -11290,38 +11748,40 @@
         <v>80</v>
       </c>
       <c r="AL65" s="52" t="s">
-        <v>208</v>
-      </c>
-      <c r="AM65" s="52" t="s">
+        <v>207</v>
+      </c>
+      <c r="AM65" s="52"/>
+      <c r="AN65" s="52"/>
+      <c r="AO65" s="52" t="s">
         <v>125</v>
       </c>
-      <c r="AN65" s="52"/>
-      <c r="AO65" s="5">
+      <c r="AP65" s="52"/>
+      <c r="AQ65" s="5">
         <v>2</v>
       </c>
-      <c r="AP65" s="57" t="s">
-        <v>632</v>
-      </c>
-      <c r="AQ65">
+      <c r="AR65" s="57" t="s">
+        <v>629</v>
+      </c>
+      <c r="AS65" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C65)</f>
-        <v>3</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A66" s="9">
         <v>203009</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F66" s="9"/>
       <c r="G66" s="5">
@@ -11336,7 +11796,7 @@
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M66" s="5"/>
       <c r="N66" s="5">
@@ -11374,36 +11834,40 @@
         <v>114</v>
       </c>
       <c r="AL66" s="52" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AM66" s="52" t="s">
         <v>117</v>
       </c>
       <c r="AN66" s="52"/>
-      <c r="AO66" s="5">
+      <c r="AO66" s="52" t="s">
+        <v>117</v>
+      </c>
+      <c r="AP66" s="52"/>
+      <c r="AQ66" s="5">
         <v>3</v>
       </c>
-      <c r="AP66" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="AQ66">
+      <c r="AR66" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="AS66" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C66)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="67" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A67" s="9">
         <v>203010</v>
       </c>
       <c r="B67" s="28" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D67" s="48"/>
       <c r="E67" s="48" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F67" s="28"/>
       <c r="G67" s="48">
@@ -11418,7 +11882,7 @@
       <c r="J67" s="48"/>
       <c r="K67" s="48"/>
       <c r="L67" s="48" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="M67" s="48"/>
       <c r="N67" s="48">
@@ -11456,41 +11920,45 @@
         <v>114</v>
       </c>
       <c r="AL67" s="54" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AM67" s="54" t="s">
         <v>117</v>
       </c>
       <c r="AN67" s="54"/>
-      <c r="AO67" s="48">
+      <c r="AO67" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="AP67" s="54"/>
+      <c r="AQ67" s="48">
         <v>2</v>
       </c>
-      <c r="AP67" s="48" t="s">
-        <v>443</v>
-      </c>
-      <c r="AQ67">
+      <c r="AR67" s="48" t="s">
+        <v>440</v>
+      </c>
+      <c r="AS67" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C67)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="68" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A68" s="12">
         <v>208001</v>
       </c>
       <c r="B68" s="14" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G68" s="5">
         <v>1</v>
@@ -11522,10 +11990,10 @@
         <v>1</v>
       </c>
       <c r="Z68" s="8" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AA68" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AB68" s="5"/>
       <c r="AC68" s="5"/>
@@ -11537,38 +12005,40 @@
       <c r="AI68" s="44"/>
       <c r="AJ68" s="44"/>
       <c r="AK68" s="5" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AL68" s="52"/>
       <c r="AM68" s="52"/>
       <c r="AN68" s="52"/>
-      <c r="AO68" s="5">
+      <c r="AO68" s="52"/>
+      <c r="AP68" s="52"/>
+      <c r="AQ68" s="5">
         <v>4</v>
       </c>
-      <c r="AP68" s="55" t="s">
-        <v>248</v>
-      </c>
-      <c r="AQ68">
+      <c r="AR68" s="55" t="s">
+        <v>245</v>
+      </c>
+      <c r="AS68" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C68)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="69" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A69" s="12">
         <v>208002</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G69" s="5">
         <v>1</v>
@@ -11609,23 +12079,25 @@
       <c r="AI69" s="44"/>
       <c r="AJ69" s="44"/>
       <c r="AK69" s="5" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AL69" s="52"/>
       <c r="AM69" s="52"/>
       <c r="AN69" s="52"/>
-      <c r="AO69" s="5">
+      <c r="AO69" s="52"/>
+      <c r="AP69" s="52"/>
+      <c r="AQ69" s="5">
         <v>2</v>
       </c>
-      <c r="AP69" s="55" t="s">
-        <v>375</v>
-      </c>
-      <c r="AQ69">
+      <c r="AR69" s="55" t="s">
+        <v>372</v>
+      </c>
+      <c r="AS69" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C69)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="70" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A70" s="12">
         <v>208003</v>
       </c>
@@ -11633,14 +12105,14 @@
         <v>94</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G70" s="5">
         <v>1</v>
@@ -11685,40 +12157,42 @@
       <c r="AI70" s="44"/>
       <c r="AJ70" s="44"/>
       <c r="AK70" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AL70" s="52"/>
       <c r="AM70" s="52"/>
       <c r="AN70" s="52"/>
-      <c r="AO70" s="5">
+      <c r="AO70" s="52"/>
+      <c r="AP70" s="52"/>
+      <c r="AQ70" s="5">
         <v>3</v>
       </c>
-      <c r="AP70" s="55" t="s">
-        <v>373</v>
-      </c>
-      <c r="AQ70">
+      <c r="AR70" s="55" t="s">
+        <v>370</v>
+      </c>
+      <c r="AS70" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C70)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="71" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A71" s="12">
         <v>208004</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="G71" s="5">
         <v>1</v>
@@ -11756,10 +12230,10 @@
         <v>1</v>
       </c>
       <c r="Z71" s="8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AA71" s="8" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="AB71" s="5"/>
       <c r="AC71" s="5"/>
@@ -11771,38 +12245,40 @@
       <c r="AI71" s="44"/>
       <c r="AJ71" s="44"/>
       <c r="AK71" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AL71" s="52"/>
       <c r="AM71" s="52"/>
       <c r="AN71" s="52"/>
-      <c r="AO71" s="5">
+      <c r="AO71" s="52"/>
+      <c r="AP71" s="52"/>
+      <c r="AQ71" s="5">
         <v>4</v>
       </c>
-      <c r="AP71" s="55" t="s">
-        <v>374</v>
-      </c>
-      <c r="AQ71">
+      <c r="AR71" s="55" t="s">
+        <v>371</v>
+      </c>
+      <c r="AS71" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C71)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="72" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A72" s="12">
         <v>208005</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G72" s="5">
         <v>1</v>
@@ -11849,40 +12325,42 @@
       <c r="AI72" s="44"/>
       <c r="AJ72" s="44"/>
       <c r="AK72" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AL72" s="52"/>
       <c r="AM72" s="52"/>
       <c r="AN72" s="52"/>
-      <c r="AO72" s="5">
+      <c r="AO72" s="52"/>
+      <c r="AP72" s="52"/>
+      <c r="AQ72" s="5">
         <v>2</v>
       </c>
-      <c r="AP72" s="55" t="s">
-        <v>376</v>
-      </c>
-      <c r="AQ72">
+      <c r="AR72" s="55" t="s">
+        <v>373</v>
+      </c>
+      <c r="AS72" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C72)</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="73" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A73" s="12">
         <v>208006</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G73" s="5">
         <v>1</v>
@@ -11920,10 +12398,10 @@
         <v>1</v>
       </c>
       <c r="Z73" s="8" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AA73" s="8" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AB73" s="5"/>
       <c r="AC73" s="5"/>
@@ -11935,38 +12413,40 @@
       <c r="AI73" s="44"/>
       <c r="AJ73" s="44"/>
       <c r="AK73" s="50" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AL73" s="52"/>
       <c r="AM73" s="52"/>
       <c r="AN73" s="52"/>
-      <c r="AO73" s="5">
+      <c r="AO73" s="52"/>
+      <c r="AP73" s="52"/>
+      <c r="AQ73" s="5">
         <v>3</v>
       </c>
-      <c r="AP73" s="55" t="s">
-        <v>460</v>
-      </c>
-      <c r="AQ73">
+      <c r="AR73" s="55" t="s">
+        <v>457</v>
+      </c>
+      <c r="AS73" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C73)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="74" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A74" s="12">
         <v>208007</v>
       </c>
       <c r="B74" s="16" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G74" s="5">
         <v>1</v>
@@ -12013,40 +12493,42 @@
       <c r="AI74" s="44"/>
       <c r="AJ74" s="44"/>
       <c r="AK74" s="50" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AL74" s="52"/>
       <c r="AM74" s="52"/>
       <c r="AN74" s="52"/>
-      <c r="AO74" s="5">
+      <c r="AO74" s="52"/>
+      <c r="AP74" s="52"/>
+      <c r="AQ74" s="5">
         <v>2</v>
       </c>
-      <c r="AP74" s="55" t="s">
-        <v>461</v>
-      </c>
-      <c r="AQ74">
+      <c r="AR74" s="55" t="s">
+        <v>458</v>
+      </c>
+      <c r="AS74" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C74)</f>
-        <v>3</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="75" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A75" s="12">
         <v>208008</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G75" s="5">
         <v>1</v>
@@ -12074,14 +12556,14 @@
         <v>3</v>
       </c>
       <c r="Z75" s="8" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="AA75" s="8"/>
       <c r="AB75" s="5"/>
       <c r="AC75" s="5"/>
       <c r="AD75" s="5"/>
       <c r="AE75" s="44" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="AF75" s="44"/>
       <c r="AG75" s="44"/>
@@ -12091,38 +12573,40 @@
       <c r="AI75" s="44"/>
       <c r="AJ75" s="44"/>
       <c r="AK75" s="59" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="AL75" s="52"/>
       <c r="AM75" s="52"/>
       <c r="AN75" s="52"/>
-      <c r="AO75" s="5">
+      <c r="AO75" s="52"/>
+      <c r="AP75" s="52"/>
+      <c r="AQ75" s="5">
         <v>2</v>
       </c>
-      <c r="AP75" s="55" t="s">
-        <v>619</v>
-      </c>
-      <c r="AQ75">
+      <c r="AR75" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="AS75" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C75)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="76" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A76" s="12">
         <v>208009</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D76" s="5"/>
       <c r="E76" s="5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G76" s="5">
         <v>1</v>
@@ -12163,35 +12647,37 @@
       <c r="AI76" s="44"/>
       <c r="AJ76" s="44"/>
       <c r="AK76" s="50" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AL76" s="52"/>
       <c r="AM76" s="52"/>
       <c r="AN76" s="52"/>
-      <c r="AO76" s="5">
+      <c r="AO76" s="52"/>
+      <c r="AP76" s="52"/>
+      <c r="AQ76" s="5">
         <v>1</v>
       </c>
-      <c r="AP76" s="55" t="s">
-        <v>473</v>
-      </c>
-      <c r="AQ76">
+      <c r="AR76" s="55" t="s">
+        <v>470</v>
+      </c>
+      <c r="AS76" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C76)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="77" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A77" s="34">
         <v>209001</v>
       </c>
       <c r="B77" s="35" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D77" s="47"/>
       <c r="E77" s="47" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="F77" s="34"/>
       <c r="G77" s="47">
@@ -12202,7 +12688,7 @@
       <c r="J77" s="47"/>
       <c r="K77" s="47"/>
       <c r="L77" s="47" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M77" s="47"/>
       <c r="N77" s="47"/>
@@ -12233,39 +12719,41 @@
       <c r="AI77" s="45"/>
       <c r="AJ77" s="45"/>
       <c r="AK77" s="47" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AL77" s="53"/>
       <c r="AM77" s="53" t="s">
         <v>68</v>
       </c>
       <c r="AN77" s="53"/>
-      <c r="AO77" s="47">
+      <c r="AO77" s="53"/>
+      <c r="AP77" s="53"/>
+      <c r="AQ77" s="47">
         <v>3</v>
       </c>
-      <c r="AP77" s="56" t="s">
+      <c r="AR77" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="AQ77">
+      <c r="AS77" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C77)</f>
-        <v>2</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="78" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A78" s="11">
         <v>209002</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F78" s="11"/>
       <c r="G78" s="5">
@@ -12276,7 +12764,7 @@
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
       <c r="L78" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M78" s="5"/>
       <c r="N78" s="5">
@@ -12307,39 +12795,41 @@
       <c r="AI78" s="44"/>
       <c r="AJ78" s="44"/>
       <c r="AK78" s="5" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AL78" s="52"/>
-      <c r="AM78" s="52" t="s">
+      <c r="AM78" s="52"/>
+      <c r="AN78" s="52"/>
+      <c r="AO78" s="52" t="s">
         <v>106</v>
       </c>
-      <c r="AN78" s="52"/>
-      <c r="AO78" s="5">
+      <c r="AP78" s="52"/>
+      <c r="AQ78" s="5">
         <v>4</v>
       </c>
-      <c r="AP78" s="55" t="s">
+      <c r="AR78" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="AQ78">
+      <c r="AS78" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C78)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="79" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A79" s="11">
         <v>209003</v>
       </c>
       <c r="B79" s="14" t="s">
+        <v>566</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="D79" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="C79" s="11" t="s">
-        <v>570</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>572</v>
-      </c>
       <c r="E79" s="5" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="F79" s="11"/>
       <c r="G79" s="5">
@@ -12383,35 +12873,37 @@
       <c r="AI79" s="44"/>
       <c r="AJ79" s="44"/>
       <c r="AK79" s="5" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="AL79" s="52"/>
       <c r="AM79" s="52"/>
       <c r="AN79" s="52"/>
-      <c r="AO79" s="5">
+      <c r="AO79" s="52"/>
+      <c r="AP79" s="52"/>
+      <c r="AQ79" s="5">
         <v>3</v>
       </c>
-      <c r="AP79" s="55" t="s">
-        <v>567</v>
-      </c>
-      <c r="AQ79">
+      <c r="AR79" s="55" t="s">
+        <v>564</v>
+      </c>
+      <c r="AS79" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C79)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="80" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A80" s="11">
         <v>209004</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D80" s="5"/>
       <c r="E80" s="5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F80" s="11"/>
       <c r="G80" s="5">
@@ -12422,7 +12914,7 @@
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
       <c r="L80" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
@@ -12453,33 +12945,35 @@
       <c r="AI80" s="44"/>
       <c r="AJ80" s="44"/>
       <c r="AK80" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="AL80" s="52"/>
-      <c r="AM80" s="52" t="s">
+      <c r="AM80" s="52"/>
+      <c r="AN80" s="52"/>
+      <c r="AO80" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="AN80" s="52"/>
-      <c r="AO80" s="5">
+      <c r="AP80" s="52"/>
+      <c r="AQ80" s="5">
         <v>2</v>
       </c>
-      <c r="AP80" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="AQ80">
+      <c r="AR80" s="55" t="s">
+        <v>327</v>
+      </c>
+      <c r="AS80" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C80)</f>
-        <v>7</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="81" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A81" s="11">
         <v>209005</v>
       </c>
       <c r="B81" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D81" s="5"/>
       <c r="E81" s="5" t="s">
@@ -12496,7 +12990,7 @@
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
       <c r="L81" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
@@ -12525,37 +13019,39 @@
       <c r="AI81" s="44"/>
       <c r="AJ81" s="44"/>
       <c r="AK81" s="5" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="AL81" s="52"/>
       <c r="AM81" s="52" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN81" s="52"/>
+      <c r="AO81" s="52"/>
+      <c r="AP81" s="52"/>
+      <c r="AQ81" s="5">
+        <v>3</v>
+      </c>
+      <c r="AR81" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="AN81" s="52"/>
-      <c r="AO81" s="5">
-        <v>3</v>
-      </c>
-      <c r="AP81" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="AQ81">
+      <c r="AS81" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C81)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="82" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A82" s="11">
         <v>209006</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D82" s="5"/>
       <c r="E82" s="5" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="F82" s="11"/>
       <c r="G82" s="5">
@@ -12566,7 +13062,7 @@
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
       <c r="L82" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M82" s="5"/>
       <c r="N82" s="5"/>
@@ -12595,37 +13091,39 @@
       <c r="AI82" s="44"/>
       <c r="AJ82" s="44"/>
       <c r="AK82" s="5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="AL82" s="52"/>
       <c r="AM82" s="52" t="s">
         <v>68</v>
       </c>
       <c r="AN82" s="52"/>
-      <c r="AO82" s="5">
+      <c r="AO82" s="52"/>
+      <c r="AP82" s="52"/>
+      <c r="AQ82" s="5">
         <v>2</v>
       </c>
-      <c r="AP82" s="55" t="s">
-        <v>578</v>
-      </c>
-      <c r="AQ82">
+      <c r="AR82" s="55" t="s">
+        <v>575</v>
+      </c>
+      <c r="AS82" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C82)</f>
-        <v>1</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="83" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A83" s="11">
         <v>209007</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D83" s="5"/>
       <c r="E83" s="47" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F83" s="11"/>
       <c r="G83" s="5">
@@ -12636,7 +13134,7 @@
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
       <c r="L83" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="M83" s="5"/>
       <c r="N83" s="5"/>
@@ -12667,37 +13165,39 @@
       <c r="AI83" s="44"/>
       <c r="AJ83" s="44"/>
       <c r="AK83" s="5" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AL83" s="52"/>
       <c r="AM83" s="52" t="s">
         <v>68</v>
       </c>
       <c r="AN83" s="52"/>
-      <c r="AO83" s="5">
+      <c r="AO83" s="52"/>
+      <c r="AP83" s="52"/>
+      <c r="AQ83" s="5">
         <v>2</v>
       </c>
-      <c r="AP83" s="55" t="s">
-        <v>315</v>
-      </c>
-      <c r="AQ83">
+      <c r="AR83" s="55" t="s">
+        <v>312</v>
+      </c>
+      <c r="AS83" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C83)</f>
-        <v>8</v>
+        <v>#VALUE!</v>
       </c>
     </row>
-    <row r="84" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A84" s="11">
         <v>209008</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D84" s="5"/>
       <c r="E84" s="5" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="F84" s="11"/>
       <c r="G84" s="5">
@@ -12708,7 +13208,7 @@
       <c r="J84" s="5"/>
       <c r="K84" s="5"/>
       <c r="L84" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="M84" s="5"/>
       <c r="N84" s="5"/>
@@ -12739,26 +13239,28 @@
       <c r="AI84" s="44"/>
       <c r="AJ84" s="44"/>
       <c r="AK84" s="5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="AL84" s="52"/>
-      <c r="AM84" s="52" t="s">
-        <v>332</v>
-      </c>
+      <c r="AM84" s="52"/>
       <c r="AN84" s="52"/>
-      <c r="AO84" s="5">
+      <c r="AO84" s="52" t="s">
+        <v>329</v>
+      </c>
+      <c r="AP84" s="52"/>
+      <c r="AQ84" s="5">
         <v>2</v>
       </c>
-      <c r="AP84" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="AQ84">
+      <c r="AR84" s="55" t="s">
+        <v>331</v>
+      </c>
+      <c r="AS84" t="e">
         <f>COUNTIF([1]Sheet1!$R:$U,C84)</f>
-        <v>5</v>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AP84">
+  <autoFilter ref="A4:AR84">
     <sortState ref="A5:AG49">
       <sortCondition ref="A4:A49"/>
     </sortState>
